--- a/backlog/Feature_Story.xlsx
+++ b/backlog/Feature_Story.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Documents\Ruchi_Office_Important\watch-datapipeline\backlog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA228170-1022-4382-B4AF-8DC23B5C67F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAC0862A-9368-47D1-99B1-808F22A0913C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10320" xr2:uid="{4CD1A7F7-4D43-438E-AADC-95F9EACC7B8E}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="464">
   <si>
     <t>Feature</t>
   </si>
@@ -805,6 +805,627 @@
   </si>
   <si>
     <t>P0,Governance,Standards,Control</t>
+  </si>
+  <si>
+    <t>P1 Collector</t>
+  </si>
+  <si>
+    <t>Collector Architecture</t>
+  </si>
+  <si>
+    <t>P1-1A</t>
+  </si>
+  <si>
+    <t>Define Collector Capability Model Supporting ADOT and Custom Collector Implementations</t>
+  </si>
+  <si>
+    <t>As a Data Engineering team, I want a collector capability model so that both ADOT and custom collectors can be supported in a pluggable manner</t>
+  </si>
+  <si>
+    <t>Define capabilities, abstraction layer, pluggability model</t>
+  </si>
+  <si>
+    <t>collector-capability-model.md</t>
+  </si>
+  <si>
+    <t>Capability model supports both implementations</t>
+  </si>
+  <si>
+    <t>Simulate switching collectors via config</t>
+  </si>
+  <si>
+    <t>P1,Collector,OTEL,ADOT,CustomCollector,Pluggability</t>
+  </si>
+  <si>
+    <t>P1-1B</t>
+  </si>
+  <si>
+    <t>Define Collector Configuration Model for Implementation Selection</t>
+  </si>
+  <si>
+    <t>As a Data Engineering team, I want a configuration model so that collector implementation can be selected dynamically</t>
+  </si>
+  <si>
+    <t>Define config-driven mechanism to switch between ADOT and custom collector without code changes</t>
+  </si>
+  <si>
+    <t>Define config schema and selection logic</t>
+  </si>
+  <si>
+    <t>collector-config-schema.yaml</t>
+  </si>
+  <si>
+    <t>Config enables switching implementations</t>
+  </si>
+  <si>
+    <t>Validate config-based switching</t>
+  </si>
+  <si>
+    <t>P1,Collector,Config,Pluggability</t>
+  </si>
+  <si>
+    <t>Ingestion &amp; API Gateway</t>
+  </si>
+  <si>
+    <t>P1-2A</t>
+  </si>
+  <si>
+    <t>Define API Gateway as Standard Ingestion Aperture for Telemetry</t>
+  </si>
+  <si>
+    <t>As a Data Engineering team, I want API Gateway as ingestion layer so that all telemetry flows through a controlled entry point</t>
+  </si>
+  <si>
+    <t>Define API Gateway as mandatory ingestion layer ensuring decoupling and governance</t>
+  </si>
+  <si>
+    <t>Define ingestion architecture and flow</t>
+  </si>
+  <si>
+    <t>ingestion-architecture.md</t>
+  </si>
+  <si>
+    <t>All ingestion routed via gateway</t>
+  </si>
+  <si>
+    <t>Validate ingestion flow</t>
+  </si>
+  <si>
+    <t>P1,API,Gateway,Ingestion,Aperture</t>
+  </si>
+  <si>
+    <t>P1-2B</t>
+  </si>
+  <si>
+    <t>Implement Terraform Modules for API Gateway Provisioning</t>
+  </si>
+  <si>
+    <t>As a Data Engineering team, I want Terraform-based API Gateway setup so that environments can be provisioned consistently</t>
+  </si>
+  <si>
+    <t>Define Terraform modules for API Gateway provisioning integrated with platform infra</t>
+  </si>
+  <si>
+    <t>Define Terraform modules and configs</t>
+  </si>
+  <si>
+    <t>Terraform scripts for API Gateway</t>
+  </si>
+  <si>
+    <t>Gateway deployable via Terraform</t>
+  </si>
+  <si>
+    <t>Deploy in test environment</t>
+  </si>
+  <si>
+    <t>P1,Terraform,API,Infra</t>
+  </si>
+  <si>
+    <t>P1-2C</t>
+  </si>
+  <si>
+    <t>Define API Gateway Routing and Throttling Rules for Telemetry Ingestion</t>
+  </si>
+  <si>
+    <t>As a Data Engineering team, I want routing and throttling rules so that ingestion is scalable and controlled</t>
+  </si>
+  <si>
+    <t>Define routing rules, rate limits, and throttling for telemetry ingestion</t>
+  </si>
+  <si>
+    <t>Define routing policies and rate limits</t>
+  </si>
+  <si>
+    <t>API gateway configuration</t>
+  </si>
+  <si>
+    <t>Rules enforce ingestion control</t>
+  </si>
+  <si>
+    <t>Validate with load simulation</t>
+  </si>
+  <si>
+    <t>P1,API,Scaling,Throttling</t>
+  </si>
+  <si>
+    <t>Collector Implementation</t>
+  </si>
+  <si>
+    <t>P1-3A</t>
+  </si>
+  <si>
+    <t>Setup ADOT Collector with Standard Configuration</t>
+  </si>
+  <si>
+    <t>As a Data Engineering team, I want ADOT collector setup so that standard telemetry ingestion is supported</t>
+  </si>
+  <si>
+    <t>Configure ADOT collector with OTEL pipelines aligned to contracts</t>
+  </si>
+  <si>
+    <t>Define pipelines and exporters</t>
+  </si>
+  <si>
+    <t>ADOT config files</t>
+  </si>
+  <si>
+    <t>ADOT collector operational</t>
+  </si>
+  <si>
+    <t>Validate ingestion pipeline</t>
+  </si>
+  <si>
+    <t>P1,ADOT,OTEL,Collector</t>
+  </si>
+  <si>
+    <t>P1-3B</t>
+  </si>
+  <si>
+    <t>Develop Custom Collector for Advanced Processing (PII Redaction, Enrichment)</t>
+  </si>
+  <si>
+    <t>As a Data Engineering team, I want custom collector so that advanced capabilities like PII redaction are supported</t>
+  </si>
+  <si>
+    <t>Implement custom collector supporting transformation, redaction, enrichment</t>
+  </si>
+  <si>
+    <t>Define processing pipeline and logic</t>
+  </si>
+  <si>
+    <t>Custom collector implementation</t>
+  </si>
+  <si>
+    <t>PII redaction and enrichment working</t>
+  </si>
+  <si>
+    <t>Validate with sample data</t>
+  </si>
+  <si>
+    <t>P1,CustomCollector,PII,Processing</t>
+  </si>
+  <si>
+    <t>P1-3C</t>
+  </si>
+  <si>
+    <t>Define Processing Pipeline for Telemetry Transformation and Routing</t>
+  </si>
+  <si>
+    <t>As a Data Engineering team, I want processing pipeline so that telemetry can be transformed and routed appropriately</t>
+  </si>
+  <si>
+    <t>Define processing stages for enrichment, filtering, routing</t>
+  </si>
+  <si>
+    <t>Processing pipeline definition</t>
+  </si>
+  <si>
+    <t>Pipeline supports transformation</t>
+  </si>
+  <si>
+    <t>Validate pipeline outputs</t>
+  </si>
+  <si>
+    <t>P1,Processing,Pipeline</t>
+  </si>
+  <si>
+    <t>Contracts &amp; Integration</t>
+  </si>
+  <si>
+    <t>P1-4A</t>
+  </si>
+  <si>
+    <t>Integrate Telemetry Contract Enforcement in Collector Pipelines</t>
+  </si>
+  <si>
+    <t>As a Data Engineering team, I want contract enforcement so that all telemetry complies with platform standards</t>
+  </si>
+  <si>
+    <t>Ensure collector validates telemetry against defined contracts before processing</t>
+  </si>
+  <si>
+    <t>Integrate validation logic</t>
+  </si>
+  <si>
+    <t>Contract validation module</t>
+  </si>
+  <si>
+    <t>Invalid telemetry rejected</t>
+  </si>
+  <si>
+    <t>Test invalid payload</t>
+  </si>
+  <si>
+    <t>P1,Contracts,Validation</t>
+  </si>
+  <si>
+    <t>P1-4B</t>
+  </si>
+  <si>
+    <t>Implement Trace Propagation Across Collector Pipelines</t>
+  </si>
+  <si>
+    <t>As a Data Engineering team, I want trace propagation so that end-to-end observability is maintained</t>
+  </si>
+  <si>
+    <t>Ensure trace_id propagation across ingestion, processing, and export</t>
+  </si>
+  <si>
+    <t>Define propagation mechanism</t>
+  </si>
+  <si>
+    <t>Trace propagation implementation</t>
+  </si>
+  <si>
+    <t>Trace continuity maintained</t>
+  </si>
+  <si>
+    <t>Validate trace flow</t>
+  </si>
+  <si>
+    <t>P1,Tracing,OTEL</t>
+  </si>
+  <si>
+    <t>Infrastructure</t>
+  </si>
+  <si>
+    <t>P1-5A</t>
+  </si>
+  <si>
+    <t>Define Terraform Modules for Collector Deployment</t>
+  </si>
+  <si>
+    <t>As a Data Engineering team, I want Terraform modules so that collector can be deployed consistently</t>
+  </si>
+  <si>
+    <t>Define reusable Terraform modules for collector infra</t>
+  </si>
+  <si>
+    <t>Define infra modules</t>
+  </si>
+  <si>
+    <t>Terraform scripts</t>
+  </si>
+  <si>
+    <t>Collector deployable via Terraform</t>
+  </si>
+  <si>
+    <t>Deploy in test env</t>
+  </si>
+  <si>
+    <t>P1,Terraform,Infra</t>
+  </si>
+  <si>
+    <t>P1-5B</t>
+  </si>
+  <si>
+    <t>Enable Dual Deployment Strategy (Embedded and Portable)</t>
+  </si>
+  <si>
+    <t>As a Data Engineering team, I want dual deployment so that both platform-managed and user-managed setups are supported</t>
+  </si>
+  <si>
+    <t>Define deployment strategies for embedded and portable setups</t>
+  </si>
+  <si>
+    <t>Define deployment modes</t>
+  </si>
+  <si>
+    <t>Deployment strategy doc</t>
+  </si>
+  <si>
+    <t>Both modes supported</t>
+  </si>
+  <si>
+    <t>Validate both deployments</t>
+  </si>
+  <si>
+    <t>P1,Deployment,Packaging</t>
+  </si>
+  <si>
+    <t>Security</t>
+  </si>
+  <si>
+    <t>P1-6A</t>
+  </si>
+  <si>
+    <t>Implement PII Detection and Redaction in Collector</t>
+  </si>
+  <si>
+    <t>As a Data Engineering team, I want PII redaction so that sensitive data is not exposed</t>
+  </si>
+  <si>
+    <t>Implement PII detection and masking in custom collector</t>
+  </si>
+  <si>
+    <t>Define detection and masking rules</t>
+  </si>
+  <si>
+    <t>PII processing module</t>
+  </si>
+  <si>
+    <t>PII properly redacted</t>
+  </si>
+  <si>
+    <t>P1,Security,PII</t>
+  </si>
+  <si>
+    <t>P1-6B</t>
+  </si>
+  <si>
+    <t>Secure Collector Endpoints and Ingestion Interfaces</t>
+  </si>
+  <si>
+    <t>As a Data Engineering team, I want secure endpoints so that ingestion is protected</t>
+  </si>
+  <si>
+    <t>Implement authentication and secure communication for collector endpoints</t>
+  </si>
+  <si>
+    <t>Define auth and encryption</t>
+  </si>
+  <si>
+    <t>Security configuration</t>
+  </si>
+  <si>
+    <t>Endpoints secured</t>
+  </si>
+  <si>
+    <t>Validate with auth tests</t>
+  </si>
+  <si>
+    <t>P1,Security,API</t>
+  </si>
+  <si>
+    <t>Define capability model covering ingestion, processing, transformation, routing, export supporting ADOT and custom collectors via configuration</t>
+  </si>
+  <si>
+    <t>Scaling &amp; Performance</t>
+  </si>
+  <si>
+    <t>P1-7A</t>
+  </si>
+  <si>
+    <t>Define Collector Horizontal Scaling Model for High-Volume Telemetry</t>
+  </si>
+  <si>
+    <t>As a Data Engineering team, I want a defined scaling model so that collector can handle varying telemetry loads without degradation</t>
+  </si>
+  <si>
+    <t>Define horizontal scaling approach including stateless design, load distribution, and scaling triggers aligned with cloud-native patterns</t>
+  </si>
+  <si>
+    <t>Define scaling architecture, stateless requirements, scaling triggers</t>
+  </si>
+  <si>
+    <t>scaling-model.md</t>
+  </si>
+  <si>
+    <t>Scaling model supports high throughput and horizontal scaling</t>
+  </si>
+  <si>
+    <t>Simulate load and validate scaling behavior</t>
+  </si>
+  <si>
+    <t>P1,Scaling,Performance,Architecture</t>
+  </si>
+  <si>
+    <t>P1-7B</t>
+  </si>
+  <si>
+    <t>Define Auto-Scaling Policies and Thresholds for Collector Infrastructure</t>
+  </si>
+  <si>
+    <t>As a Data Engineering team, I want auto-scaling policies so that collector dynamically adapts to workload</t>
+  </si>
+  <si>
+    <t>Define CPU, memory, throughput-based scaling thresholds and policies using Terraform/cloud configs</t>
+  </si>
+  <si>
+    <t>Define thresholds, policies, scaling rules</t>
+  </si>
+  <si>
+    <t>autoscaling-config.yaml</t>
+  </si>
+  <si>
+    <t>Auto-scaling triggers correctly based on load</t>
+  </si>
+  <si>
+    <t>Validate scaling under simulated load</t>
+  </si>
+  <si>
+    <t>P1,Scaling,Infra,Automation</t>
+  </si>
+  <si>
+    <t>Export &amp; Integration</t>
+  </si>
+  <si>
+    <t>P1-7C</t>
+  </si>
+  <si>
+    <t>Define Standard Export Contracts for Telemetry Delivery to Downstream Systems</t>
+  </si>
+  <si>
+    <t>As a Data Engineering team, I want export contracts so that telemetry is delivered consistently to downstream systems</t>
+  </si>
+  <si>
+    <t>Define contract for exporting logs, metrics, and traces ensuring compatibility with observability backends</t>
+  </si>
+  <si>
+    <t>Define export schema, formats, endpoints</t>
+  </si>
+  <si>
+    <t>export-contract.yaml</t>
+  </si>
+  <si>
+    <t>Export conforms to defined contract</t>
+  </si>
+  <si>
+    <t>Validate data in downstream system</t>
+  </si>
+  <si>
+    <t>P1,Export,Contracts,Integration</t>
+  </si>
+  <si>
+    <t>P1-7D</t>
+  </si>
+  <si>
+    <t>Implement Config-Driven Multi-Destination Telemetry Routing</t>
+  </si>
+  <si>
+    <t>As a Data Engineering team, I want configurable routing so that telemetry can be sent to multiple systems without code changes</t>
+  </si>
+  <si>
+    <t>Enable routing rules to direct telemetry to multiple destinations based on config and metadata</t>
+  </si>
+  <si>
+    <t>Define routing rules and config model</t>
+  </si>
+  <si>
+    <t>routing-config.yaml</t>
+  </si>
+  <si>
+    <t>Telemetry routed to multiple destinations correctly</t>
+  </si>
+  <si>
+    <t>Validate routing across endpoints</t>
+  </si>
+  <si>
+    <t>P1,Routing,Export,Config</t>
+  </si>
+  <si>
+    <t>Observability of Collector</t>
+  </si>
+  <si>
+    <t>P1-8A</t>
+  </si>
+  <si>
+    <t>Enable Self-Observability for Collector Components</t>
+  </si>
+  <si>
+    <t>As a Data Engineering team, I want collector to emit its own telemetry so that its health and behavior are observable</t>
+  </si>
+  <si>
+    <t>Instrument collector to emit metrics, logs, and traces aligned with telemetry contracts</t>
+  </si>
+  <si>
+    <t>Define self-observability signals</t>
+  </si>
+  <si>
+    <t>collector-observability-config</t>
+  </si>
+  <si>
+    <t>Collector emits internal telemetry</t>
+  </si>
+  <si>
+    <t>Validate collector metrics and traces</t>
+  </si>
+  <si>
+    <t>P1,Observability,Monitoring,Collector</t>
+  </si>
+  <si>
+    <t>P1-8B</t>
+  </si>
+  <si>
+    <t>Define Standard Health and Performance Metrics for Collector Monitoring</t>
+  </si>
+  <si>
+    <t>As a Data Engineering team, I want standardized metrics so that collector health can be monitored consistently</t>
+  </si>
+  <si>
+    <t>Define metrics like latency, throughput, error rate, and queue depth for monitoring</t>
+  </si>
+  <si>
+    <t>Define metric definitions and thresholds</t>
+  </si>
+  <si>
+    <t>health-metrics-definition.md</t>
+  </si>
+  <si>
+    <t>Metrics available and consistent</t>
+  </si>
+  <si>
+    <t>Validate metrics in monitoring system</t>
+  </si>
+  <si>
+    <t>P1,Monitoring,Health,Metrics</t>
+  </si>
+  <si>
+    <t>Resilience</t>
+  </si>
+  <si>
+    <t>P1-9A</t>
+  </si>
+  <si>
+    <t>Define Retry and Error Handling Strategy for Collector Pipelines</t>
+  </si>
+  <si>
+    <t>As a Data Engineering team, I want retry strategy so that transient failures do not cause data loss</t>
+  </si>
+  <si>
+    <t>Define retry logic, exponential backoff, and failure handling patterns for ingestion and processing</t>
+  </si>
+  <si>
+    <t>Define retry policies and error handling rules</t>
+  </si>
+  <si>
+    <t>retry-strategy.md</t>
+  </si>
+  <si>
+    <t>Retry mechanism handles transient failures</t>
+  </si>
+  <si>
+    <t>Simulate failure scenarios</t>
+  </si>
+  <si>
+    <t>P1,Resilience,Retry,ErrorHandling</t>
+  </si>
+  <si>
+    <t>P1-9B</t>
+  </si>
+  <si>
+    <t>Implement Buffering and Backpressure Handling Mechanisms</t>
+  </si>
+  <si>
+    <t>As a Data Engineering team, I want buffering so that burst traffic is handled without data loss or overload</t>
+  </si>
+  <si>
+    <t>Define buffering strategies, queueing mechanisms, and backpressure handling aligned with scaling model</t>
+  </si>
+  <si>
+    <t>Define buffering and queue strategies</t>
+  </si>
+  <si>
+    <t>buffering-config.yaml</t>
+  </si>
+  <si>
+    <t>No data loss under burst load</t>
+  </si>
+  <si>
+    <t>Load test with burst traffic</t>
+  </si>
+  <si>
+    <t>P1,Resilience,Buffering,Scaling</t>
   </si>
 </sst>
 </file>
@@ -855,7 +1476,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -863,6 +1484,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1177,19 +1799,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3594F0E7-7C10-4023-9C47-66514D348C6C}">
-  <dimension ref="A1:L28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:L50"/>
+  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="9.140625" customWidth="1"/>
-    <col min="4" max="4" width="32.140625" customWidth="1"/>
-    <col min="5" max="5" width="40.7109375" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" customWidth="1"/>
-    <col min="8" max="10" width="9.140625" customWidth="1"/>
-    <col min="12" max="12" width="9.140625" customWidth="1"/>
+    <col min="1" max="2" width="9.140625" style="3"/>
+    <col min="3" max="3" width="9.140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="32.140625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="40.7109375" style="3" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="12.7109375" style="3" customWidth="1"/>
+    <col min="8" max="10" width="9.140625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="9.140625" style="3"/>
+    <col min="12" max="12" width="9.140625" style="3" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1227,7 +1852,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" ht="78.75" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -1265,7 +1890,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="56.25" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -1303,7 +1928,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" ht="45" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -1341,7 +1966,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" ht="45" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -1379,7 +2004,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" ht="45" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -1417,7 +2042,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="45" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -1455,7 +2080,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" ht="45" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -1493,7 +2118,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
@@ -1531,7 +2156,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
@@ -1569,7 +2194,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -1607,7 +2232,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
@@ -1645,7 +2270,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" ht="45" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>10</v>
       </c>
@@ -1683,7 +2308,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>10</v>
       </c>
@@ -1721,7 +2346,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" ht="45" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>10</v>
       </c>
@@ -1759,7 +2384,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>10</v>
       </c>
@@ -1797,7 +2422,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>10</v>
       </c>
@@ -1835,7 +2460,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>10</v>
       </c>
@@ -1873,7 +2498,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" ht="45" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>10</v>
       </c>
@@ -1911,7 +2536,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>10</v>
       </c>
@@ -1949,7 +2574,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>10</v>
       </c>
@@ -1987,7 +2612,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>10</v>
       </c>
@@ -2025,7 +2650,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="101.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" ht="101.25" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>10</v>
       </c>
@@ -2063,7 +2688,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" ht="90" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>10</v>
       </c>
@@ -2101,7 +2726,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" ht="78.75" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>10</v>
       </c>
@@ -2139,7 +2764,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" ht="67.5" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>10</v>
       </c>
@@ -2177,7 +2802,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" ht="56.25" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>10</v>
       </c>
@@ -2215,7 +2840,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" ht="78.75" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>10</v>
       </c>
@@ -2251,6 +2876,842 @@
       </c>
       <c r="L28" s="2" t="s">
         <v>256</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="101.25" x14ac:dyDescent="0.2">
+      <c r="A29" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="K29" s="2">
+        <v>1</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="67.5" x14ac:dyDescent="0.2">
+      <c r="A30" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="K30" s="2">
+        <v>1</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="56.25" x14ac:dyDescent="0.2">
+      <c r="A31" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="K31" s="2">
+        <v>1</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="67.5" x14ac:dyDescent="0.2">
+      <c r="A32" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="K32" s="2">
+        <v>1</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A33" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="K33" s="2">
+        <v>1</v>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A34" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="K34" s="2">
+        <v>1</v>
+      </c>
+      <c r="L34" s="2" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="56.25" x14ac:dyDescent="0.2">
+      <c r="A35" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="K35" s="2">
+        <v>1</v>
+      </c>
+      <c r="L35" s="2" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A36" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="K36" s="2">
+        <v>1</v>
+      </c>
+      <c r="L36" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="56.25" x14ac:dyDescent="0.2">
+      <c r="A37" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K37" s="2">
+        <v>1</v>
+      </c>
+      <c r="L37" s="2" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="56.25" x14ac:dyDescent="0.2">
+      <c r="A38" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="K38" s="2">
+        <v>1</v>
+      </c>
+      <c r="L38" s="2" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A39" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="K39" s="2">
+        <v>1</v>
+      </c>
+      <c r="L39" s="2" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A40" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="K40" s="2">
+        <v>1</v>
+      </c>
+      <c r="L40" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A41" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="K41" s="2">
+        <v>1</v>
+      </c>
+      <c r="L41" s="2" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" ht="56.25" x14ac:dyDescent="0.2">
+      <c r="A42" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="K42" s="2">
+        <v>1</v>
+      </c>
+      <c r="L42" s="2" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" ht="90" x14ac:dyDescent="0.2">
+      <c r="A43" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="K43" s="2">
+        <v>1</v>
+      </c>
+      <c r="L43" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="78.75" x14ac:dyDescent="0.2">
+      <c r="A44" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="K44" s="2">
+        <v>1</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" ht="78.75" x14ac:dyDescent="0.2">
+      <c r="A45" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="J45" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="K45" s="2">
+        <v>1</v>
+      </c>
+      <c r="L45" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" ht="67.5" x14ac:dyDescent="0.2">
+      <c r="A46" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="K46" s="2">
+        <v>1</v>
+      </c>
+      <c r="L46" s="2" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" ht="56.25" x14ac:dyDescent="0.2">
+      <c r="A47" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="J47" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="K47" s="2">
+        <v>1</v>
+      </c>
+      <c r="L47" s="2" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" ht="56.25" x14ac:dyDescent="0.2">
+      <c r="A48" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="K48" s="2">
+        <v>1</v>
+      </c>
+      <c r="L48" s="2" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" ht="67.5" x14ac:dyDescent="0.2">
+      <c r="A49" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="I49" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="J49" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="K49" s="2">
+        <v>1</v>
+      </c>
+      <c r="L49" s="2" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" ht="67.5" x14ac:dyDescent="0.2">
+      <c r="A50" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="J50" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="K50" s="2">
+        <v>1</v>
+      </c>
+      <c r="L50" s="2" t="s">
+        <v>463</v>
       </c>
     </row>
   </sheetData>

--- a/backlog/Feature_Story.xlsx
+++ b/backlog/Feature_Story.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Documents\Ruchi_Office_Important\watch-datapipeline\backlog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAC0862A-9368-47D1-99B1-808F22A0913C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDBF29C9-D9AA-452C-8914-E68594DED01C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10320" xr2:uid="{4CD1A7F7-4D43-438E-AADC-95F9EACC7B8E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$70</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -34,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2146" uniqueCount="1709">
   <si>
     <t>Feature</t>
   </si>
@@ -1426,6 +1429,3741 @@
   </si>
   <si>
     <t>P1,Resilience,Buffering,Scaling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P2 Airflow </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Instrumentation </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P2-1A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define Airflow Telemetry Model Aligned with Platform Contracts </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want a telemetry model for Airflow so that orchestration data aligns with platform contracts </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define telemetry structure for DAGs, tasks, runs aligned with telemetry contract without restricting extensibility </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define DAG, task, run level attributes </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> airflow-telemetry-model.md </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Telemetry aligns with platform contract </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate sample DAG telemetry </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P2,Airflow,Telemetry,Contracts</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P2-1B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Implement DAG-Level Telemetry Emission </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want DAG-level telemetry so that workflow execution is observable </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Instrument Airflow to emit telemetry for DAG start, end, status, duration </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define DAG-level signals </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> DAG telemetry implementation </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> DAG events captured correctly </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate DAG execution logs </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P2,Airflow,DAG,Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P2-1C </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Implement Task-Level Telemetry Emission </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want task-level telemetry so that granular execution visibility is available </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Emit telemetry for each task including status, retries, duration </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define task-level signals </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Task telemetry implementation </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Task-level visibility available </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate task execution data </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P2,Airflow,Task,Telemetry</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P2-1D </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Enable Custom Metadata Propagation in Airflow Telemetry </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want custom metadata support so that business context can flow through telemetry </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Allow injection of custom attributes without schema restriction </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define extensible metadata model </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Metadata propagation config </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Custom attributes visible in telemetry </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate custom metadata flow </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P2,Airflow,Metadata,Extensibility</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Integration </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P2-2A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Integrate Airflow Telemetry with Collector via API Gateway </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want Airflow to send telemetry via collector so that ingestion is standardized </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Configure Airflow to send telemetry to collector through API Gateway using defined contracts </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define integration flow and config </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Integration configuration </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Telemetry reaches collector correctly </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate ingestion pipeline </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P2,Airflow,Collector,Integration</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P2-2B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ensure Contract Compliance for Airflow Telemetry </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want Airflow telemetry to comply with contracts so that integration is seamless </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate Airflow telemetry against telemetry contract before ingestion </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define validation rules </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Contract validation integration </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Non-compliant telemetry rejected </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Test invalid payload </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P2,Airflow,Contracts,Validation</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Tracing </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P2-3A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Implement End-to-End Trace Propagation Across Airflow DAGs </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want trace propagation so that workflows can be traced end-to-end </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ensure trace_id flows across DAGs, tasks, and downstream systems </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define trace propagation logic </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Trace propagation implementation </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Trace continuity maintained </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate trace across tasks </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P2,Airflow,Tracing,OTEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P2-3B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Correlate Airflow Execution with Downstream Systems </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want correlation so that orchestration connects with processing layers </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Enable trace linkage between Airflow and downstream systems using shared identifiers </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define correlation strategy </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Correlation configuration </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Cross-system trace linkage works </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate multi-system trace </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P2,Airflow,Tracing,Integration</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Multi-Granularity </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P2-4A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Support Multi-Layer Telemetry Emission from Airflow </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want multi-layer telemetry so that both technical and business context is captured </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ensure Airflow emits both orchestration and business-level signals without restriction </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define multi-layer telemetry model </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Multi-layer telemetry config </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Both layers visible in output </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate telemetry richness </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P2,Airflow,Telemetry,Business</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P2-4B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Enable Dataset and Pipeline-Level Context in Airflow Telemetry </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want dataset-level context so that business impact is visible </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Add dataset, pipeline, domain identifiers into telemetry </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define business context attributes </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Context mapping config </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Dataset-level visibility achieved </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate dataset tracking </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P2,Airflow,DataProduct,Context</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Infrastructure </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P2-5A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define Terraform Modules for Airflow Observability Enablement </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want Terraform modules so that Airflow observability setup is standardized </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define infra setup for enabling observability in Airflow environments </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define Terraform configs </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Terraform scripts </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Setup deployable via Terraform </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Deploy in test env </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P2,Airflow,Terraform,Infra</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P2-5B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Enable Default Observability in New Airflow Environments </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want observability enabled by default so that new environments are compliant </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Integrate observability setup into base environment provisioning </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define default configs </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Environment provisioning config </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Observability auto-enabled </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate new environment setup </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P2,Airflow,Deployment,Default</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Observability </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P2-6A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define Airflow-Specific Metrics for Monitoring and Alerting </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want Airflow metrics so that orchestration health is visible </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define metrics like DAG success rate, task failures, latency </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define metrics schema </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Metrics definition doc </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Metrics available for dashboards </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate metrics in monitoring system </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P2,Airflow,Metrics,Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P2-6B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Enable Logging Integration for Airflow Tasks </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want logs integrated so that debugging is easier </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ensure Airflow logs are captured and routed via collector </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define logging integration </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Logging config </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Logs available centrally </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate log ingestion </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P2,Airflow,Logs,Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Resilience </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P2-7A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Handle Failures and Retries in Airflow Telemetry Consistently </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want failure handling captured so that retries and failures are visible </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ensure retries and failures are correctly reflected in telemetry </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define retry and failure signals </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Retry telemetry config </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Failures visible in telemetry </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Simulate retry scenarios </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P2,Airflow,Resilience</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P2-7B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ensure Idempotent Telemetry Emission from Airflow </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want idempotent telemetry so that duplicate signals do not affect observability </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ensure telemetry emission avoids duplication during retries </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define idempotency rules </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Idempotency config </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> No duplicate telemetry </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate duplicate scenarios </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P2,Airflow,Idempotency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P3 Kafka </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P3-1A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define Kafka Telemetry Model Aligned with Platform Contracts </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want a telemetry model for Kafka so that streaming data aligns with platform contracts </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define telemetry structure for topics, partitions, producers, consumers aligned with contract without restricting extensibility </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define topic, partition, producer, consumer attributes </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> kafka-telemetry-model.md </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate sample Kafka telemetry </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P3,Kafka,Telemetry,Contracts</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P3-1B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Implement Producer-Level Telemetry Emission </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want producer telemetry so that data production is observable </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Emit telemetry for producer events including throughput, errors, latency </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define producer-level signals </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Producer telemetry implementation </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Producer metrics captured correctly </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate producer metrics </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P3,Kafka,Producer,Telemetry</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P3-1C </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Implement Consumer-Level Telemetry Emission </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want consumer telemetry so that data consumption is observable </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Emit telemetry for consumer lag, throughput, failures </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define consumer-level signals </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Consumer telemetry implementation </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Consumer metrics available </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate consumer behavior </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P3,Kafka,Consumer,Telemetry</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P3-1D </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Enable Custom Metadata Propagation in Kafka Messages </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want metadata propagation so that business context flows through streams </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Allow injection of metadata (dataset, pipeline, domain) in message headers without schema restriction </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define metadata model and headers </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Metadata visible across pipeline </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate metadata propagation </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P3,Kafka,Metadata,Extensibility</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P3-2A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Integrate Kafka Telemetry with Collector via API Gateway </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want Kafka telemetry routed through collector so ingestion is standardized </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Configure producers/consumers to emit telemetry via API Gateway to collector </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define integration flow and configs </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate ingestion </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P3,Kafka,Collector,Integration</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P3-2B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ensure Contract Compliance for Kafka Telemetry </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want Kafka telemetry to comply with contracts so integration is seamless </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate Kafka telemetry against platform contracts before ingestion </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Invalid telemetry rejected </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P3,Kafka,Contracts,Validation</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P3-3A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Implement End-to-End Trace Propagation in Kafka Streams </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want trace propagation so that streaming pipelines are traceable end-to-end </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ensure trace_id flows through producers, topics, partitions, consumers </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define trace propagation mechanism </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate trace across systems </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P3,Kafka,Tracing,OTEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P3-3B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Correlate Kafka Streams with Upstream and Downstream Systems </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want correlation so that Kafka connects orchestration and processing layers </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Enable linkage between Kafka, Airflow, Spark using shared identifiers </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Cross-system trace works </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate end-to-end trace </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P3,Kafka,Tracing,Integration</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P3-4A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Support Multi-Layer Telemetry in Kafka (Infra + Business Context) </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want multi-layer telemetry so that both infra and business signals are captured </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ensure Kafka emits infra metrics and business context without restriction </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Both layers visible </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P3,Kafka,Telemetry,Business</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P3-4B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Enable Dataset and Event-Level Context in Kafka Telemetry </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want dataset-level context so business impact is visible </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Add dataset, event type, domain context to telemetry </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define business attributes </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Dataset/event visibility achieved </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P3,Kafka,DataProduct,Context</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P3-5A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define Terraform Modules for Kafka Observability Enablement </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want Terraform modules so Kafka observability setup is standardized </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define infra setup for enabling Kafka observability </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P3,Kafka,Terraform,Infra</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P3-5B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Enable Default Observability in Kafka Environments </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want observability enabled by default so new environments are compliant </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Integrate observability setup into Kafka environment provisioning </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Environment config </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate environment setup </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P3,Kafka,Deployment,Default</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P3-6A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define Kafka-Specific Metrics for Monitoring and Alerting </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want Kafka metrics so streaming health is visible </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define metrics like consumer lag, throughput, partition skew </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Metrics available </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P3,Kafka,Metrics,Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P3-6B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Enable Logging Integration for Kafka Producers and Consumers </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want logs integrated so debugging is easier </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ensure Kafka logs are captured and routed via collector </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P3,Kafka,Logs,Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Scaling &amp; Performance </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P3-7A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define Partitioning and Throughput Strategy for Kafka Topics </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want partitioning strategy so Kafka scales efficiently </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define partitioning, replication, throughput optimization strategy </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define topic configuration </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Partitioning strategy doc </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Topics scale efficiently </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate throughput </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P3,Kafka,Scaling,Performance</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P3-7B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Monitor and Optimize Consumer Lag and Throughput </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want lag monitoring so performance bottlenecks are visible </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define lag monitoring and optimization strategies </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define monitoring approach </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Lag monitoring config </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Lag metrics visible and optimized </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate lag scenarios </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P3,Kafka,Lag,Performance</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P3-8A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Implement Retry and Failure Handling in Kafka Pipelines </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want retry mechanisms so transient failures are handled </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define retry logic for producers and consumers </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define retry policies </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Retry configuration </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Failures handled gracefully </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Simulate failures </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P3,Kafka,Resilience,Retry</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P3-8B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ensure Exactly-Once or Idempotent Processing in Kafka Pipelines </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want idempotent processing so duplicates are avoided </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define idempotency and exactly-once semantics where applicable </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define idempotency strategy </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> No duplicate processing </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P3,Kafka,Idempotency,Processing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P4 Spark/Glue </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P4-1A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define Spark/Glue Telemetry Model Aligned with Platform Contracts </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want a telemetry model for Spark/Glue so that processing layer aligns with platform contracts </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define telemetry structure for jobs, stages, tasks, datasets aligned with contracts without restricting extensibility </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define job, stage, task, dataset attributes </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> spark-telemetry-model.md </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate sample job telemetry </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P4,Spark,Glue,Telemetry,Contracts</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P4-1B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Implement Job-Level Telemetry Emission for Spark/Glue </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want job-level telemetry so that processing execution is observable </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Emit telemetry for job start, end, status, duration </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define job-level signals </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Job telemetry implementation </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Job events captured correctly </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate job execution </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P4,Spark,Glue,Job,Telemetry</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P4-1C </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Implement Stage and Task-Level Telemetry Emission </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want stage/task telemetry so that granular execution visibility is available </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Emit telemetry for stages and tasks including performance metrics </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define stage/task signals </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Stage/task telemetry config </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Granular visibility available </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate execution metrics </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P4,Spark,Glue,Task,Telemetry</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P4-1D </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Enable Business-Level Metadata Propagation in Processing Jobs </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want business metadata propagation so that business context is captured </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Allow injection of dataset, domain, product metadata into telemetry without restriction </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define metadata model </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Business metadata visible </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate metadata flow </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P4,Spark,Glue,Business,Metadata</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P4-2A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Integrate Spark/Glue Telemetry with Collector via API Gateway </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want processing telemetry routed via collector so ingestion is standardized </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Configure Spark/Glue jobs to emit telemetry via API Gateway to collector </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P4,Spark,Glue,Collector,Integration</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P4-2B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ensure Contract Compliance for Processing Telemetry </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want telemetry to comply with contracts so integration is seamless </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate Spark/Glue telemetry against platform contracts before ingestion </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P4,Spark,Glue,Contracts,Validation</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P4-3A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Implement End-to-End Trace Propagation in Processing Pipelines </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want trace propagation so that processing is traceable end-to-end </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ensure trace_id flows across jobs, stages, tasks and integrates with upstream/downstream </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Trace implementation </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate trace flow </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P4,Spark,Glue,Tracing,OTEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P4-3B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Correlate Processing Jobs with Orchestration and Streaming Layers </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want correlation so that processing connects with Airflow and Kafka </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Enable linkage between Spark/Glue, Airflow, Kafka via shared identifiers </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Correlation config </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate end-to-end flow </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P4,Spark,Glue,Tracing,Integration</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P4-4A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Support Multi-Layer Telemetry (Infra + Processing + Business) </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want multi-layer telemetry so that all levels are observable </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ensure telemetry captures infra metrics, processing metrics, and business signals </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define multi-layer model </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> All layers visible </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P4,Spark,Glue,Telemetry,Business</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P4-4B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Enable Dataset-Level and Data Product Context in Telemetry </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Add dataset, data product, domain attributes to telemetry </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define context attributes </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Dataset visibility achieved </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate dataset lineage signals </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P4,Spark,Glue,DataProduct,Context</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P4-5A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define Terraform Modules for Spark/Glue Observability Enablement </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want Terraform modules so observability setup is standardized </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define infra setup for enabling observability in Spark/Glue environments </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P4,Spark,Glue,Terraform,Infra</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P4-5B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Enable Default Observability in Processing Environments </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Integrate observability setup into environment provisioning </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P4,Spark,Glue,Deployment,Default</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P4-6A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define Processing Metrics for Monitoring and Optimization </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want processing metrics so performance and cost are visible </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define metrics like job duration, stage time, resource usage, data volume </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P4,Spark,Glue,Metrics,Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P4-6B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Enable Logging Integration for Processing Jobs </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ensure logs from Spark/Glue are captured and routed via collector </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P4,Spark,Glue,Logs,Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Data Quality &amp; Semantics </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P4-7A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Capture Data Quality Signals in Telemetry </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want data quality signals so pipeline health includes data correctness </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Emit metrics for nulls, schema drift, validation failures </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define quality signals </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Data quality config </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Quality signals visible </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate with test data </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P4,Spark,Glue,DataQuality</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P4-7B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Capture Schema and Data Drift Indicators in Telemetry </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want drift indicators so changes in data are observable </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Detect and emit schema and distribution drift signals </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define drift detection rules </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Drift config </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Drift signals available </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate drift scenarios </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P4,Spark,Glue,DataDrift</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P4-8A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Handle Failures and Retries in Processing Telemetry </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want failure visibility so retries and issues are traceable </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ensure retries, failures, and recovery are captured in telemetry </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define retry signals </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Failures visible </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Simulate failure scenarios </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P4,Spark,Glue,Resilience</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P4-8B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ensure Idempotent Telemetry Emission for Processing Jobs </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want idempotent telemetry so duplicate signals do not distort insights </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P4,Spark,Glue,Idempotency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P5 Dashboard </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Foundation </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P5-1A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define Dashboarding Philosophy and Persona-Based Visualization Model </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want a dashboarding model so that different stakeholders can view observability data relevant to them </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define persona-driven dashboarding approach covering leadership, platform, domain, and operational users without enforcing rigid structure </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define personas and visualization principles </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> dashboarding-model.md </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Personas and views clearly defined </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate mapping of personas to dashboards </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P5,Dashboard,Design,Persona</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P5-1B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define Flexible Dashboard Organization Model (Non-Rigid Hierarchy) </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want flexible dashboard organization so that structure evolves with use cases </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define indicative but non-mandatory hierarchy (system, domain, data product, pipeline) allowing extensibility </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define logical grouping model </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> dashboard-structure.md </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Structure supports flexibility </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate with sample dashboards </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P5,Dashboard,Structure,Extensibility</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P5-2A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define Data Model for Dashboard Consumption from Observability Platform </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want a unified data model so that dashboards consume telemetry consistently </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define how metrics, logs, and traces are aggregated and exposed for dashboarding </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define aggregation and query model </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> dashboard-data-model.md </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Data model supports all layers </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate sample queries </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P5,Dashboard,DataModel,Integration</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P5-2B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Integrate Dashboard Layer with Observability Data Sources </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want dashboards integrated with telemetry sources so that data is visualized correctly </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Connect dashboards to collector outputs and observability backends </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define integration configs </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Integration setup </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Dashboards show correct data </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate dashboard outputs </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P5,Dashboard,Integration,Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Persona Views </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P5-3A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Build Executive-Level Dashboard for Data Marketplace Health </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a leadership stakeholder, I want a high-level dashboard so that I can assess overall data marketplace health </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Create dashboard showing data product health, pipeline status, SLA, failures at aggregated level </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define executive KPIs </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Executive dashboard </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Leadership view available </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate KPI visibility </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P5,Dashboard,Leadership,Marketplace</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P5-3B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Build Platform-Level Dashboard for System Observability </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a platform lead, I want platform-level dashboard so that system health is visible </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Create dashboards for infra, ingestion, pipeline health across systems </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define platform metrics </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Platform dashboard </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Platform metrics visible </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate system monitoring </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P5,Dashboard,Platform,Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P5-3C </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Build Domain-Level Dashboard for Business Units </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a domain owner, I want domain-level dashboard so that my data products are observable </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Create dashboards grouped by domain showing pipelines, datasets, issues </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define domain metrics </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Domain dashboard </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Domain-level visibility achieved </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate domain mapping </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P5,Dashboard,Domain,Business</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P5-3D </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Build Data Product-Level Dashboard for Dataset Observability </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a data product owner, I want product-level dashboard so that dataset health is visible </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Create dashboards showing dataset freshness, quality, lineage signals </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define dataset metrics </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Data product dashboard </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Dataset health visible </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate dataset metrics </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P5,Dashboard,DataProduct</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P5-3E </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Build Pipeline-Level Dashboard for Operational Monitoring </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a support engineer, I want pipeline-level dashboard so that I can debug issues </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Create dashboards showing DAGs, jobs, Kafka flows, failures, retries </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define pipeline metrics </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Pipeline dashboard </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Pipeline details visible </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate debugging scenarios </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P5,Dashboard,Pipeline,Operations</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Visualization </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P5-4A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define Standard Visualization Components and Patterns </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want standard visual components so that dashboards are consistent </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define charts, graphs, heatmaps, trace views for observability data </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define visualization standards </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Visualization guidelines </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Consistent visuals across dashboards </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate UI consistency </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P5,Dashboard,UI,Visualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P5-4B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Enable Drill-Down and Navigation Across Dashboard Layers </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a user, I want drill-down capability so that I can move from high-level to detailed views </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Enable navigation from marketplace → domain → product → pipeline </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define navigation model </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Drill-down configuration </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Navigation works across layers </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate navigation flow </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P5,Dashboard,Navigation,UX</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P5-5A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Support Multi-Layer Visualization (Infra, Orchestration, Processing, Business) </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want multi-layer dashboards so that all levels are visible </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ensure dashboards can show infra, orchestration, processing, and business signals </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define multi-layer mapping </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Multi-layer dashboard config </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate across layers </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P5,Dashboard,Telemetry,Business</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P5-5B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Correlate Metrics, Logs, and Traces in Dashboards </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want correlated views so that issues can be analyzed holistically </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Enable linking metrics, logs, traces in dashboards </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define correlation model </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Correlation setup </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Cross-signal correlation works </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate correlation scenarios </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P5,Dashboard,Tracing,Correlation</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P5-6A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define Dashboard Provisioning via Infrastructure as Code </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want dashboards provisioned via IaC so that setup is repeatable </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define Terraform or config-based dashboard provisioning </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define provisioning configs </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Terraform/dashboard configs </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Dashboards deployable via IaC </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P5,Dashboard,Terraform,Infra</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P5-6B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Enable Default Dashboard Setup for New Environments </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want default dashboards so that new environments are usable immediately </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Integrate dashboard setup into environment provisioning </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define default dashboards </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Dashboards auto-created </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate new environment </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P5,Dashboard,Deployment,Default</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> UX &amp; Adoption </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P5-7A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Design User-Friendly Dashboard Navigation and Experience </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a user, I want intuitive dashboards so that adoption is easy </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define UX principles, naming conventions, navigation simplicity </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define UX guidelines </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> UX design doc </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Easy navigation and usage </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> User validation </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P5,Dashboard,UX,Adoption</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P5-7B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Provide Dashboard Templates for Rapid Adoption </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want reusable templates so that dashboards can be created quickly </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define templates for common use cases (pipeline, dataset, platform) </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define template library </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Dashboard templates </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Templates reusable </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate template usage </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P5,Dashboard,Templates,Adoption</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P6 Alerting </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P6-1A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define Alerting Philosophy and Multi-Layer Signal Strategy </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want an alerting model so that signals are meaningful and actionable across layers </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define alerting principles covering infra, orchestration, processing, and business signals with focus on signal-to-noise optimization </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define alerting principles and layers </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> alerting-model.md </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Alerting model clearly defined </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate mapping of signals to alerts </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P6,Alerting,Design,Strategy</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P6-1B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define Alert Severity and Classification Framework </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want alert classification so that alerts are prioritized correctly </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define severity levels (critical, high, medium, low) and classification rules for different signal types </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define severity model and thresholds </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> alert-severity-model.md </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Alerts categorized consistently </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate severity mapping </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P6,Alerting,Severity,Standards</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P6-2A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define Alert Generation Model from Observability Signals </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want alerts generated from telemetry so that issues are detected automatically </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define how metrics, logs, and traces trigger alerts based on rules and thresholds </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define alert rules and triggers </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> alert-rules-config.yaml </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Alerts generated correctly from signals </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate alert triggering </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P6,Alerting,Integration,Rules</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P6-2B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Integrate Alerting System with Observability Data Sources </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want alerting integrated with observability platform so that signals flow seamlessly </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Connect alerting system with metrics, logs, traces pipelines </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Alerts triggered from all sources </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate alert flow </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P6,Alerting,Integration,Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> SLO/SLA </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P6-3A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define SLO and SLA Model for Data Pipelines and Products </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want SLO definitions so that reliability is measurable </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define SLOs for pipelines, datasets, freshness, latency, success rates </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define SLO model </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> slo-definition.md </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> SLOs defined for key entities </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate SLO definitions </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P6,SLO,SLA,Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P6-3B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Implement SLO-Based Alerting for Breach Detection </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want SLO-based alerts so that breaches are detected proactively </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Trigger alerts when SLO thresholds are violated across pipelines and datasets </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define SLO alert rules </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> SLO alert config </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Alerts triggered on breach </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Simulate SLA breach </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P6,SLO,Alerting,Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Persona Alerts </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P6-4A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define Persona-Based Alert Routing Strategy </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want alert routing so that alerts reach the right stakeholders </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define routing rules for leadership, platform, domain, and support teams </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define routing model </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> alert-routing.md </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Alerts routed correctly </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate routing paths </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P6,Alerting,Routing,Persona</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P6-4B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Implement Notification Channels for Alerts </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want notifications so that alerts are delivered via appropriate channels </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Integrate alerting with email, Slack, incident tools for notification delivery </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define notification configs </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Notification setup </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Alerts delivered to users </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate notification delivery </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P6,Alerting,Notifications</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Intelligence </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P6-5A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Implement Noise Reduction and Alert Deduplication Logic </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want reduced alert noise so that teams focus on important issues </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define deduplication, suppression, and aggregation rules for alerts </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define noise reduction rules </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Deduplication config </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Reduced duplicate alerts </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate noise scenarios </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P6,Alerting,Optimization</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P6-5B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Implement Correlation-Based Alerting Across Systems </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want correlated alerts so that root cause is easier to identify </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Correlate alerts across Airflow, Kafka, Spark to identify root causes </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define correlation logic </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Related alerts grouped </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P6,Alerting,Correlation</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P6-5C </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Enable Context-Enriched Alerts with Business and Technical Metadata </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want enriched alerts so that debugging is faster </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Include dataset, pipeline, domain, trace context in alert payloads </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define enrichment model </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Alert enrichment config </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Alerts include full context </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate enriched alerts </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P6,Alerting,Context</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P6-6A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define Alerting Infrastructure Provisioning via IaC </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want alerting setup via IaC so that environments are consistent </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define Terraform or config-based provisioning for alerting systems </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define infra configs </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Alerting infra deployable </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P6,Alerting,Terraform,Infra</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P6-6B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Enable Default Alerting Setup for New Environments </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want alerting enabled by default so that new environments are monitored </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Integrate alerting setup into environment provisioning </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define default alerts </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Alerts auto-enabled </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate new setup </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P6,Alerting,Deployment,Default</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P6-7A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Design Alert Dashboard and Incident View </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a user, I want a consolidated alert view so that I can track incidents effectively </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Create dashboard for alerts, incidents, status, and resolution tracking </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define alert dashboard model </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Alert dashboard </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Alerts visible in dashboard </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate dashboard usability </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P6,Alerting,Dashboard,UX</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P6-7B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define Alert Playbooks and Response Guidelines </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want playbooks so that alerts are handled consistently </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define response steps, escalation paths, and resolution guidelines for alerts </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define playbook structure </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Alert playbooks </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Playbooks available for alerts </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate response flow </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P6,Alerting,Playbook,Operations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P7 Packaging </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P7-1A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define Observability Package Structure and Distribution Model </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want a packaging model so that observability solution can be distributed and reused </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define overall package structure including modules, configs, and dependencies for distribution across teams </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define package structure and components </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> packaging-model.md </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Package structure clearly defined </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate with sample packaging </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P7,Packaging,Design</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P7-1B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define Packaging Strategy for Embedded and Portable Deployments </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want packaging strategy so that solution works in both platform-managed and user-managed environments </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define approach for embedded (default infra) and portable (external infra) deployment models </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define packaging modes </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> packaging-strategy.md </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Both deployment modes supported </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate both setups </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P7,Packaging,Deployment</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Build &amp; Distribution </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P7-2A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Create Modular Packaging for Observability Components </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want modular packages so that components can be reused independently </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Package collector, Airflow, Kafka, Spark modules independently with clear boundaries </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define module packaging </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Modular packages </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Modules independently usable </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate module reuse </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P7,Packaging,Modules</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P7-2B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define Versioning Strategy for Observability Packages </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want versioning so that package releases are traceable and compatible </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define versioning for modules and overall package ensuring compatibility with contracts </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define versioning rules </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> versioning-model.md </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Versioning consistent across modules </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate version upgrades </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P7,Packaging,Versioning</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P7-2C </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Enable Distribution of Observability Package via Git-Based Repository </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want package distributed via Git so that teams can access and reuse it easily </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define Git-based distribution model including repo structure and access patterns </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define distribution model </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Repository setup </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Package accessible via Git </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate package access </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P7,Packaging,Distribution,Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P7-3A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define Plug-and-Play Integration Model for New Technologies </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want plug-and-play model so that new technologies can be integrated easily </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define how new modules can plug into observability platform via contracts and configs </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define integration model </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> plugin-integration.md </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> New modules integrate without breaking system </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate with sample plugin </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P7,Packaging,Extensibility</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P7-3B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Provide Standard Configuration Templates for Easy Integration </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want config templates so that integration is simple and consistent </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define reusable configuration templates for onboarding new systems </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define config templates </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Template configs </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P7,Packaging,Config</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Deployment </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P7-4A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Enable One-Click Deployment for Observability Package </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want simplified deployment so that setup is quick and easy </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Provide scripts or commands for deploying full observability stack </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define deployment scripts </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Deployment scripts </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Package deployable with minimal steps </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate deployment flow </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P7-4B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Integrate Package Deployment with Existing Environment Provisioning </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want package integrated with infra provisioning so that setup is seamless </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ensure observability package integrates with Terraform-based environment provisioning </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define integration approach </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Infra integration config </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Package auto-deployed with environment </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate provisioning flow </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P7,Packaging,Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Usability </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P7-5A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Provide Clear Installation and Setup Documentation </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want clear documentation so that teams can adopt the package easily </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Create installation guides and setup steps for users </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define documentation structure </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Setup documentation </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Docs easy to follow </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate with user onboarding </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P7,Packaging,Docs</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P7-5B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Provide Example Implementations and Reference Use Cases </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want examples so that users understand how to use the package </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Provide sample implementations for Airflow, Kafka, Spark integrations </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define reference examples </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Example implementations </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Examples usable by teams </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate with sample usage </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P7,Packaging,Examples</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Governance </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P7-6A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define Compatibility and Upgrade Strategy for Packages </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want upgrade strategy so that package evolution does not break existing systems </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define backward compatibility and upgrade rules for packages and modules </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define compatibility rules </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> compatibility-model.md </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Upgrades do not break systems </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate upgrade scenarios </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P7,Packaging,Compatibility</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P7-6B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define Release and Distribution Workflow for Observability Package </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want release workflow so that package updates are managed consistently </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define release process including tagging, publishing, and version rollout </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define release workflow </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Release process doc </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Releases follow defined process </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate release flow </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P7,Packaging,Release</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P8 Testing </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P8-1A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define End-to-End Testing Strategy for Observability Platform </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want a testing strategy so that observability system is validated end-to-end </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define testing approach covering unit, integration, contract, and end-to-end validation across all layers </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define testing scope and layers </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> testing-strategy.md </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Strategy covers all components </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate with sample plan </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P8,Testing,Strategy</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P8-1B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define Test Data and Simulation Strategy for Telemetry Validation </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want test data strategy so that telemetry flows can be validated reliably </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define synthetic data generation and simulation of telemetry across systems </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define test scenarios and datasets </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> test-data-strategy.md </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Test data supports all scenarios </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate simulated flows </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P8,Testing,Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P8-2A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Implement Contract Testing for Telemetry Validation </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want contract testing so that telemetry conforms to defined schemas </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate telemetry against contracts for logs, metrics, traces before ingestion </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define contract test cases </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Contract test suite </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Test with invalid payloads </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P8,Testing,Contracts</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P8-2B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Implement Integration Testing Across Observability Components </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want integration testing so that all components work together </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate integration between collector, Airflow, Kafka, Spark, dashboards </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define integration scenarios </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Integration test suite </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Components work together correctly </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Run integration tests </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P8,Testing,Integration</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> End-to-End </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P8-3A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Implement End-to-End Testing for Telemetry Flow Across Systems </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want E2E testing so that telemetry flows correctly across all layers </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate full flow from source systems to dashboards and alerts </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define E2E scenarios </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> E2E test suite </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Telemetry flows end-to-end correctly </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Run full pipeline tests </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P8,Testing,E2E</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P8-3B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate Multi-Layer Telemetry Consistency Across Systems </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want consistency validation so that telemetry across layers is coherent </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ensure infra, orchestration, processing, and business signals are consistent </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Consistency test config </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Signals consistent across layers </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate cross-layer data </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P8,Testing,Consistency</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Performance </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P8-4A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define Load Testing Strategy for High-Volume Telemetry </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want load testing so that system handles scale </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define load scenarios for high throughput telemetry ingestion and processing </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define load scenarios </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> load-testing-plan.md </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Load scenarios defined </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate plan execution </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P8,Testing,Performance</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P8-4B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Execute Load and Stress Tests for Observability Platform </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want load testing executed so that performance bottlenecks are identified </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Simulate high-volume telemetry and stress conditions across system </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Execute load tests </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Load test results </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> System handles expected load </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Analyze performance metrics </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P8-5A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Simulate Failure Scenarios Across Observability Components </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want failure testing so that system resilience is validated </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Simulate failures in collector, pipelines, ingestion, and downstream systems </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define failure scenarios </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Failure test suite </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate failure recovery </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P8,Testing,Resilience</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P8-5B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate Retry, Recovery, and Data Loss Prevention Mechanisms </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want recovery validation so that no data is lost during failures </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Test retry, buffering, and recovery mechanisms across pipelines </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define recovery tests </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Recovery validation config </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> No data loss observed </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate retry scenarios </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P8,Testing,Recovery</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Automation </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P8-6A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Integrate Automated Testing into CI/CD Pipeline </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want automated testing so that quality checks run continuously </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Integrate unit, integration, contract, and E2E tests into CI/CD pipelines </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define CI test stages </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> CI test config </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Tests run automatically </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate CI pipeline </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P8,Testing,CI</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P8-6B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Enforce Quality Gates Based on Test Outcomes </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want quality gates so that only validated changes are deployed </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define pass/fail criteria for tests and enforce in pipeline </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define quality thresholds </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Quality gate config </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Pipeline blocks failed builds </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Test failure scenarios </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P8,Testing,Quality</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P9 CI/CD </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P9-1A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define CI/CD Strategy for Observability Platform </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want a CI/CD strategy so that build, test, and deployment are standardized across all components </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define CI/CD approach covering build, test, security, and deployment pipelines aligned with modular architecture </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define pipeline stages and flow </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cicd-strategy.md </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Strategy covers all modules </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate with sample pipeline </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P9,CI,Strategy</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P9-1B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define Branching and Release Management Model </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want a branching model so that development and releases are controlled and traceable </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define branching strategy, release flow, and merge policies aligned with inner sourcing model </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define branching rules </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> branching-model.md </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Branching model followed consistently </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate merge workflows </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P9,CI,Branching,Release</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Build </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P9-2A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Implement Build Pipelines for Observability Modules </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want automated builds so that modules are packaged consistently </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define build pipelines for collector, Airflow, Kafka, Spark, dashboards modules </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define build steps </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Build pipeline config </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Builds triggered automatically </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate build outputs </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P9,CI,Build</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P9-2B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Implement Artifact Packaging and Storage Strategy </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want artifact management so that builds are stored and versioned properly </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define artifact repository and storage approach for packages </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define artifact structure </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Artifact storage setup </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Artifacts stored and retrievable </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate artifact access </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P9,CI,Artifacts</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Testing Integration </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P9-3A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Integrate Testing Pipelines into CI/CD Workflow </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want testing integrated so that builds are validated automatically </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Integrate unit, integration, contract, and E2E tests into CI pipelines </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define test stages </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> CI test pipeline </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Tests executed in pipeline </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate test execution </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P9,CI,Testing</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P9-3B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Enforce Quality Gates Based on Test and Coverage Metrics </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want quality gates so that only validated builds are promoted </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define thresholds for test pass rate and coverage </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define quality rules </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Builds blocked on failure </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate failure scenarios </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P9,CI,Quality</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Security </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P9-4A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Integrate Security Scanning into CI/CD Pipeline </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want security scanning so that vulnerabilities are detected early </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Integrate SAST, dependency scanning, and vulnerability checks into pipeline </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define security checks </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Security scan config </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Vulnerabilities detected and reported </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate scan results </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P9,Security,CI</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P9-4B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Enforce Security Gates for Vulnerability Compliance </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want security gates so that insecure builds are blocked </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define thresholds for vulnerabilities and enforce blocking rules </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define security thresholds </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Security gate config </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Builds blocked on critical issues </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate security failures </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P9,Security,Compliance</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P9-5A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define Deployment Pipeline for Observability Platform </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want deployment pipelines so that releases are automated and consistent </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define deployment flow for environments (dev, test, prod) using IaC </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define deployment stages </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Deployment pipeline config </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Deployments automated </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P9,CI,Deployment</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P9-5B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Enable Environment-Specific Configuration Management </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want environment configs so that deployments adapt to environments </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define config management for dev, test, prod environments </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define config strategy </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Environment config setup </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Config applied per environment </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate environment configs </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P9,CI,Config</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P9-6A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define Approval and Promotion Workflow for Releases </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want approval workflow so that releases are controlled </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define manual/automated approvals and promotion rules across environments </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define approval model </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Approval workflow config </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Releases follow approval process </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate promotion flow </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P9,CI,Governance</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P9-6B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Enable Audit Logging for CI/CD Activities </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want audit logs so that changes are traceable </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Capture logs for builds, deployments, approvals, and changes </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define logging model </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Audit logging setup </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> All activities logged </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate audit trails </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P9,CI,Audit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P10 Adoption </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P10-1A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define Observability Adoption Strategy and Rollout Plan </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want an adoption strategy so that observability platform is rolled out effectively across teams </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define phased rollout plan, onboarding approach, and adoption milestones aligned with data marketplace vision </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define rollout phases and milestones </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> adoption-strategy.md </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Strategy clearly defined </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate rollout plan </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P10,Adoption,Strategy</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P10-1B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define Target User Personas and Adoption Journeys </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want defined personas so that onboarding is tailored to different users </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Identify personas (L1/L2/L3, platform, domain, leadership) and define their adoption journeys </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define personas and journeys </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> persona-adoption.md </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Personas mapped to journeys </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate persona flows </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P10,Adoption,Persona</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Onboarding </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P10-2A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Create Step-by-Step Onboarding Guides for New Teams </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Provide structured guides for integrating Airflow, Kafka, Spark with observability platform </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define onboarding steps </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> onboarding-guide.md </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Guides easy to follow </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate onboarding with new user </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P10,Adoption,Onboarding</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P10-2B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Provide Quickstart Templates for Rapid Integration </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want quickstart templates so that teams can onboard quickly </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Provide pre-configured templates for common use cases and pipelines </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define quickstart templates </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Template repository </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Templates usable directly </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P10,Adoption,Templates</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Documentation </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P10-3A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Create Comprehensive Documentation for Observability Platform </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want documentation so that users understand system capabilities and usage </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Provide documentation covering architecture, setup, usage, and troubleshooting </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Documentation portal </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Docs complete and accessible </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate documentation usability </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P10,Adoption,Docs</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P10-3B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Provide Contextual Documentation for Each Module </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want module-level docs so that each component is understandable independently </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Provide context.md, integration.md, and usage docs per module </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define module docs </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Module documentation </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Docs available per module </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate module understanding </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P10,Adoption,Modules</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Enablement </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P10-4A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Conduct Training Sessions for Observability Platform Usage </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want training so that users understand how to use the platform effectively </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Design and deliver training sessions for different personas </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define training content </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Training materials </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Training delivered successfully </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Collect feedback </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P10,Adoption,Training</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P10-4B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Create Knowledge Base and FAQs for Common Issues </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want a knowledge base so that users can resolve issues quickly </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Document FAQs, common issues, and solutions for observability platform </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define knowledge base </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> FAQ repository </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> FAQs available </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate issue resolution </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P10,Adoption,Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Support </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P10-5A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define Support and Escalation Model for Observability Platform </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want support model so that issues are handled efficiently </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define L1/L2/L3 support roles, escalation paths, and ownership </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define support structure </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> support-model.md </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Support roles clearly defined </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate escalation scenarios </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P10-5B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Implement Feedback Loop for Continuous Improvement </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want feedback loop so that platform evolves based on user input </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Capture feedback from users and incorporate into backlog and improvements </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define feedback process </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Feedback system </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Feedback captured and tracked </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate feedback cycle </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P10,Adoption,Feedback</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P10-6A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define Adoption Metrics and Success KPIs </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want adoption metrics so that platform success is measurable </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define KPIs like usage, onboarding rate, coverage, and impact </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define KPI model </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> adoption-metrics.md </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Metrics defined and tracked </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate KPI reporting </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P10,Adoption,Metrics</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P10-6B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Monitor Adoption and Drive Continuous Engagement </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want adoption monitoring so that usage grows consistently </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Track adoption metrics and drive engagement initiatives across teams </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Adoption dashboard </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Adoption trends visible </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate engagement improvement </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P10,Adoption,Engagement</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want onboarding guides so that new users can adopt the platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P11 Data Product </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P11-1A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define Data Product Model and Semantic Layer for Observability </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want a data product model so that observability is aligned with business entities </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define data product abstraction including datasets, pipelines, owners, domains and relationships across systems </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define semantic model and entities </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> data-product-model.md </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Model clearly defines data product structure </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate mapping with sample products </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P11,DataProduct,Semantic,Design</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P11-1B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define Ownership and Responsibility Mapping for Data Products </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want ownership mapping so that accountability is clear </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define mapping of data products to owners, teams, and domains for observability and alerting </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define ownership schema </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ownership-model.md </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ownership clearly defined </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate ownership mapping </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P11,DataProduct,Ownership</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P11-2A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Map Technical Pipelines to Data Products Across Systems </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want pipeline-to-product mapping so that observability reflects business context </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Map Airflow DAGs, Kafka topics, Spark jobs to data products using metadata and contracts </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define mapping model </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> mapping-config.yaml </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Pipelines mapped to products correctly </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate mapping accuracy </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P11,DataProduct,Integration</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P11-2B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Integrate Data Product Context into Telemetry Across Layers </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want product context in telemetry so that signals are business-aware </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ensure data product identifiers propagate through collector, pipelines, and dashboards </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define propagation model </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Context propagation config </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Product context visible in telemetry </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate context flow </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P11,DataProduct,Telemetry</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P11-3A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define Data Product Health Metrics and KPIs </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want product-level KPIs so that business health is measurable </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define KPIs like freshness, completeness, success rate, latency, quality for data products </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> product-kpis.md </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> KPIs defined and measurable </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate KPI calculations </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P11,DataProduct,Metrics</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P11-3B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Aggregate Multi-Layer Signals into Data Product Health Score </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want health scoring so that product status is easily understood </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Aggregate infra, orchestration, processing, and business signals into a unified health score </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define aggregation logic </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Health score config </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Health score computed correctly </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate score calculation </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P11,DataProduct,Health</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P11-4A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Build Data Product-Centric Dashboards </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a data product owner, I want product-centric dashboards so that I can monitor my data products </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Create dashboards focused on product health, datasets, pipelines, and issues </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define dashboard model </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Data product dashboards </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Product view available </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P11,Dashboard,DataProduct</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P11-4B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Enable Drill-Down from Data Product to Pipeline and Dataset Views </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a user, I want drill-down so that I can navigate from product to technical details </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Enable navigation from product to domain to pipeline to dataset to task level </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Drill-down config </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P11,Dashboard,Navigation</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Alerting </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P11-5A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Enable Data Product-Level Alerting Based on Business KPIs </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want product-level alerts so that business impact is visible </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Trigger alerts based on product KPIs like freshness, failure rate, SLA breach </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define alert rules </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Product alert config </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Alerts triggered correctly </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate alert scenarios </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P11,Alerting,DataProduct</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P11-5B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Route Alerts to Data Product Owners and Stakeholders </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want alerts routed to owners so that accountability is enforced </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ensure alerts are sent to product owners, domain leads, and stakeholders </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define routing rules </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Alert routing config </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Alerts reach correct users </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate routing </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P11,Alerting,Ownership</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P11-6A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define Data Product Lifecycle and State Model </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want lifecycle states so that product maturity and status are tracked </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define states like active, deprecated, experimental and their observability implications </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define lifecycle model </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> lifecycle-model.md </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Lifecycle states defined </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate lifecycle transitions </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P11,DataProduct,Governance</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P11-6B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Track Data Product Adoption and Usage Metrics </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a Data Engineering team, I want usage metrics so that product adoption is measurable </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Track usage, access patterns, and consumption metrics for data products </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Define usage model </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> usage-metrics.md </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Usage metrics available </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validate usage tracking </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P11,DataProduct,Adoption</t>
   </si>
 </sst>
 </file>
@@ -1484,7 +5222,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1799,14 +5539,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3594F0E7-7C10-4023-9C47-66514D348C6C}">
-  <dimension ref="A1:L50"/>
+  <dimension ref="A1:L196"/>
   <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="9.140625" style="3"/>
+    <col min="1" max="1" width="9.140625" style="3"/>
+    <col min="2" max="2" width="10.5703125" style="3" customWidth="1"/>
     <col min="3" max="3" width="9.140625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="32.140625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="40.7109375" style="3" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="23.28515625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="35.5703125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="22.140625" style="3" customWidth="1"/>
     <col min="7" max="7" width="12.7109375" style="3" customWidth="1"/>
     <col min="8" max="10" width="9.140625" style="3" customWidth="1"/>
     <col min="11" max="11" width="9.140625" style="3"/>
@@ -1852,7 +5593,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="78.75" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" ht="45" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -1890,7 +5631,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="56.25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" ht="45" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -2422,7 +6163,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>10</v>
       </c>
@@ -2650,7 +6391,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="101.25" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" ht="67.5" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>10</v>
       </c>
@@ -2688,7 +6429,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="90" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" ht="78.75" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>10</v>
       </c>
@@ -2726,7 +6467,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="78.75" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" ht="67.5" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>10</v>
       </c>
@@ -2764,7 +6505,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="67.5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12" ht="56.25" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>10</v>
       </c>
@@ -2840,7 +6581,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="78.75" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12" ht="56.25" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>10</v>
       </c>
@@ -2878,7 +6619,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="101.25" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12" ht="67.5" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>257</v>
       </c>
@@ -2916,7 +6657,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="67.5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12" ht="56.25" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>257</v>
       </c>
@@ -2954,7 +6695,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="56.25" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12" ht="45" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>257</v>
       </c>
@@ -2992,7 +6733,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="67.5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12" ht="45" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>257</v>
       </c>
@@ -3068,7 +6809,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:12" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>257</v>
       </c>
@@ -3182,7 +6923,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="56.25" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:12" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>257</v>
       </c>
@@ -3372,7 +7113,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="56.25" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:12" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>257</v>
       </c>
@@ -3448,7 +7189,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="78.75" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:12" ht="67.5" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
         <v>257</v>
       </c>
@@ -3486,7 +7227,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="78.75" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:12" ht="45" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
         <v>257</v>
       </c>
@@ -3524,7 +7265,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="67.5" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:12" ht="56.25" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>257</v>
       </c>
@@ -3562,7 +7303,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="47" spans="1:12" ht="56.25" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:12" ht="45" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
         <v>257</v>
       </c>
@@ -3600,7 +7341,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="56.25" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:12" ht="45" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
         <v>257</v>
       </c>
@@ -3638,7 +7379,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="67.5" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:12" ht="56.25" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
         <v>257</v>
       </c>
@@ -3676,7 +7417,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="67.5" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:12" ht="45" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
         <v>257</v>
       </c>
@@ -3714,7 +7455,5518 @@
         <v>463</v>
       </c>
     </row>
+    <row r="51" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A51" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="J51" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="K51" s="3">
+        <v>1</v>
+      </c>
+      <c r="L51" s="3" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A52" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="K52" s="3">
+        <v>1</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A53" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="K53" s="3">
+        <v>1</v>
+      </c>
+      <c r="L53" s="3" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A54" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="K54" s="3">
+        <v>1</v>
+      </c>
+      <c r="L54" s="3" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A55" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="I55" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="J55" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="K55" s="3">
+        <v>1</v>
+      </c>
+      <c r="L55" s="3" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A56" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="J56" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="K56" s="3">
+        <v>1</v>
+      </c>
+      <c r="L56" s="3" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" ht="56.25" x14ac:dyDescent="0.2">
+      <c r="A57" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="K57" s="3">
+        <v>1</v>
+      </c>
+      <c r="L57" s="3" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" ht="56.25" x14ac:dyDescent="0.2">
+      <c r="A58" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="K58" s="3">
+        <v>1</v>
+      </c>
+      <c r="L58" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A59" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>541</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="K59" s="3">
+        <v>1</v>
+      </c>
+      <c r="L59" s="3" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A60" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="K60" s="3">
+        <v>1</v>
+      </c>
+      <c r="L60" s="3" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A61" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="I61" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="J61" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="K61" s="3">
+        <v>1</v>
+      </c>
+      <c r="L61" s="3" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" ht="56.25" x14ac:dyDescent="0.2">
+      <c r="A62" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="K62" s="3">
+        <v>1</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A63" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="I63" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="J63" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="K63" s="3">
+        <v>1</v>
+      </c>
+      <c r="L63" s="3" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A64" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>588</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>591</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="J64" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="K64" s="3">
+        <v>1</v>
+      </c>
+      <c r="L64" s="3" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" ht="33.75" x14ac:dyDescent="0.2">
+      <c r="A65" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="I65" s="3" t="s">
+        <v>604</v>
+      </c>
+      <c r="J65" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="K65" s="3">
+        <v>1</v>
+      </c>
+      <c r="L65" s="3" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A66" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>610</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>612</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="K66" s="3">
+        <v>1</v>
+      </c>
+      <c r="L66" s="3" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" ht="56.25" x14ac:dyDescent="0.2">
+      <c r="A67" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>617</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>618</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>619</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>621</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>622</v>
+      </c>
+      <c r="I67" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="J67" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="K67" s="3">
+        <v>1</v>
+      </c>
+      <c r="L67" s="3" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A68" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>625</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>628</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>629</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>630</v>
+      </c>
+      <c r="I68" s="3" t="s">
+        <v>631</v>
+      </c>
+      <c r="J68" s="3" t="s">
+        <v>632</v>
+      </c>
+      <c r="K68" s="3">
+        <v>1</v>
+      </c>
+      <c r="L68" s="3" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A69" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>636</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>638</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>639</v>
+      </c>
+      <c r="I69" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="J69" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="K69" s="3">
+        <v>1</v>
+      </c>
+      <c r="L69" s="3" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A70" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>643</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>647</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="I70" s="3" t="s">
+        <v>648</v>
+      </c>
+      <c r="J70" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="K70" s="3">
+        <v>1</v>
+      </c>
+      <c r="L70" s="3" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A71" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>651</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>654</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>655</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="I71" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="J71" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="K71" s="3">
+        <v>1</v>
+      </c>
+      <c r="L71" s="3" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A72" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>658</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>659</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>661</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>662</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="K72" s="3">
+        <v>1</v>
+      </c>
+      <c r="L72" s="3" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" ht="56.25" x14ac:dyDescent="0.2">
+      <c r="A74" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>664</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>665</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>666</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>667</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="I74" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="J74" s="3" t="s">
+        <v>669</v>
+      </c>
+      <c r="K74" s="3">
+        <v>1</v>
+      </c>
+      <c r="L74" s="3" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A75" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>672</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>673</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="I75" s="3" t="s">
+        <v>675</v>
+      </c>
+      <c r="J75" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="K75" s="3">
+        <v>1</v>
+      </c>
+      <c r="L75" s="3" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A76" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>678</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>679</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>680</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>681</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>682</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="K76" s="3">
+        <v>1</v>
+      </c>
+      <c r="L76" s="3" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" ht="56.25" x14ac:dyDescent="0.2">
+      <c r="A77" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>684</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>685</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>686</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>687</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>688</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="I77" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="J77" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="K77" s="3">
+        <v>1</v>
+      </c>
+      <c r="L77" s="3" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A78" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>691</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>693</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>694</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="J78" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="K78" s="3">
+        <v>1</v>
+      </c>
+      <c r="L78" s="3" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A79" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>697</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>698</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>699</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="I79" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="J79" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="K79" s="3">
+        <v>1</v>
+      </c>
+      <c r="L79" s="3" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A80" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>703</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>704</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>706</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="I80" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="J80" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="K80" s="3">
+        <v>1</v>
+      </c>
+      <c r="L80" s="3" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A81" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>710</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>712</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="K81" s="3">
+        <v>1</v>
+      </c>
+      <c r="L81" s="3" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A82" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>714</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>715</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>716</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>717</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>718</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>720</v>
+      </c>
+      <c r="I82" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="J82" s="3" t="s">
+        <v>722</v>
+      </c>
+      <c r="K82" s="3">
+        <v>1</v>
+      </c>
+      <c r="L82" s="3" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A83" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>714</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>724</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>725</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>726</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>729</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>730</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>731</v>
+      </c>
+      <c r="K83" s="3">
+        <v>1</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A84" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>733</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>734</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>735</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>736</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>737</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>738</v>
+      </c>
+      <c r="I84" s="3" t="s">
+        <v>739</v>
+      </c>
+      <c r="J84" s="3" t="s">
+        <v>740</v>
+      </c>
+      <c r="K84" s="3">
+        <v>1</v>
+      </c>
+      <c r="L84" s="3" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A85" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>742</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>744</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>745</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>746</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>612</v>
+      </c>
+      <c r="I85" s="3" t="s">
+        <v>747</v>
+      </c>
+      <c r="J85" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="K85" s="3">
+        <v>1</v>
+      </c>
+      <c r="L85" s="3" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" ht="56.25" x14ac:dyDescent="0.2">
+      <c r="A86" s="3" t="s">
+        <v>749</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>750</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>751</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>752</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>755</v>
+      </c>
+      <c r="I86" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="J86" s="3" t="s">
+        <v>756</v>
+      </c>
+      <c r="K86" s="3">
+        <v>1</v>
+      </c>
+      <c r="L86" s="3" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A87" s="3" t="s">
+        <v>749</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>758</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>759</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>760</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>762</v>
+      </c>
+      <c r="H87" s="3" t="s">
+        <v>763</v>
+      </c>
+      <c r="I87" s="3" t="s">
+        <v>764</v>
+      </c>
+      <c r="J87" s="3" t="s">
+        <v>765</v>
+      </c>
+      <c r="K87" s="3">
+        <v>1</v>
+      </c>
+      <c r="L87" s="3" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A88" s="3" t="s">
+        <v>749</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>767</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>768</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>771</v>
+      </c>
+      <c r="H88" s="3" t="s">
+        <v>772</v>
+      </c>
+      <c r="I88" s="3" t="s">
+        <v>773</v>
+      </c>
+      <c r="J88" s="3" t="s">
+        <v>774</v>
+      </c>
+      <c r="K88" s="3">
+        <v>1</v>
+      </c>
+      <c r="L88" s="3" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A89" s="3" t="s">
+        <v>749</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>776</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>777</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>778</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>779</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>780</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>781</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>782</v>
+      </c>
+      <c r="K89" s="3">
+        <v>1</v>
+      </c>
+      <c r="L89" s="3" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" ht="56.25" x14ac:dyDescent="0.2">
+      <c r="A90" s="3" t="s">
+        <v>749</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>784</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>785</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>786</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>787</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>655</v>
+      </c>
+      <c r="H90" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="I90" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="J90" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="K90" s="3">
+        <v>1</v>
+      </c>
+      <c r="L90" s="3" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A91" s="3" t="s">
+        <v>749</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>789</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>790</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>791</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>792</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>662</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="K91" s="3">
+        <v>1</v>
+      </c>
+      <c r="L91" s="3" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A92" s="3" t="s">
+        <v>749</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>794</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>795</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>796</v>
+      </c>
+      <c r="F92" s="3" t="s">
+        <v>797</v>
+      </c>
+      <c r="G92" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="H92" s="3" t="s">
+        <v>798</v>
+      </c>
+      <c r="I92" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="J92" s="3" t="s">
+        <v>799</v>
+      </c>
+      <c r="K92" s="3">
+        <v>1</v>
+      </c>
+      <c r="L92" s="3" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A93" s="3" t="s">
+        <v>749</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>801</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>802</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>803</v>
+      </c>
+      <c r="F93" s="3" t="s">
+        <v>804</v>
+      </c>
+      <c r="G93" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="H93" s="3" t="s">
+        <v>805</v>
+      </c>
+      <c r="I93" s="3" t="s">
+        <v>675</v>
+      </c>
+      <c r="J93" s="3" t="s">
+        <v>806</v>
+      </c>
+      <c r="K93" s="3">
+        <v>1</v>
+      </c>
+      <c r="L93" s="3" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A94" s="3" t="s">
+        <v>749</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>808</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>809</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>810</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>811</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>812</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>813</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="K94" s="3">
+        <v>1</v>
+      </c>
+      <c r="L94" s="3" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" ht="56.25" x14ac:dyDescent="0.2">
+      <c r="A95" s="3" t="s">
+        <v>749</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>815</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>816</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>686</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>817</v>
+      </c>
+      <c r="G95" s="3" t="s">
+        <v>818</v>
+      </c>
+      <c r="H95" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="I95" s="3" t="s">
+        <v>819</v>
+      </c>
+      <c r="J95" s="3" t="s">
+        <v>820</v>
+      </c>
+      <c r="K95" s="3">
+        <v>1</v>
+      </c>
+      <c r="L95" s="3" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A96" s="3" t="s">
+        <v>749</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>822</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>823</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>824</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>825</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="K96" s="3">
+        <v>1</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A97" s="3" t="s">
+        <v>749</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>827</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>828</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>698</v>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>829</v>
+      </c>
+      <c r="G97" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="H97" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="I97" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="J97" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="K97" s="3">
+        <v>1</v>
+      </c>
+      <c r="L97" s="3" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A98" s="3" t="s">
+        <v>749</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>831</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>832</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>833</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>834</v>
+      </c>
+      <c r="G98" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="H98" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="I98" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="J98" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="K98" s="3">
+        <v>1</v>
+      </c>
+      <c r="L98" s="3" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A99" s="3" t="s">
+        <v>749</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>836</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>837</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>838</v>
+      </c>
+      <c r="G99" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="H99" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="I99" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="J99" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="K99" s="3">
+        <v>1</v>
+      </c>
+      <c r="L99" s="3" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A100" s="3" t="s">
+        <v>749</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>840</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>841</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>842</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>843</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>844</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>845</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>846</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>847</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>848</v>
+      </c>
+      <c r="K100" s="3">
+        <v>1</v>
+      </c>
+      <c r="L100" s="3" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A101" s="3" t="s">
+        <v>749</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>840</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>850</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>851</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>852</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>853</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>854</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>855</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>856</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>857</v>
+      </c>
+      <c r="K101" s="3">
+        <v>1</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A102" s="3" t="s">
+        <v>749</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>859</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>860</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>861</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>862</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>863</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>864</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>865</v>
+      </c>
+      <c r="K102" s="3">
+        <v>1</v>
+      </c>
+      <c r="L102" s="3" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A103" s="3" t="s">
+        <v>749</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>867</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>868</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>869</v>
+      </c>
+      <c r="F103" s="3" t="s">
+        <v>610</v>
+      </c>
+      <c r="G103" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="H103" s="3" t="s">
+        <v>612</v>
+      </c>
+      <c r="I103" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="J103" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="K103" s="3">
+        <v>1</v>
+      </c>
+      <c r="L103" s="3" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" ht="67.5" x14ac:dyDescent="0.2">
+      <c r="A104" s="3" t="s">
+        <v>871</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>872</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>873</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>874</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>875</v>
+      </c>
+      <c r="F104" s="3" t="s">
+        <v>876</v>
+      </c>
+      <c r="G104" s="3" t="s">
+        <v>877</v>
+      </c>
+      <c r="H104" s="3" t="s">
+        <v>878</v>
+      </c>
+      <c r="I104" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="J104" s="3" t="s">
+        <v>880</v>
+      </c>
+      <c r="K104" s="3">
+        <v>1</v>
+      </c>
+      <c r="L104" s="3" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" ht="56.25" x14ac:dyDescent="0.2">
+      <c r="A105" s="3" t="s">
+        <v>871</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>872</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>882</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>883</v>
+      </c>
+      <c r="E105" s="3" t="s">
+        <v>884</v>
+      </c>
+      <c r="F105" s="3" t="s">
+        <v>885</v>
+      </c>
+      <c r="G105" s="3" t="s">
+        <v>886</v>
+      </c>
+      <c r="H105" s="3" t="s">
+        <v>887</v>
+      </c>
+      <c r="I105" s="3" t="s">
+        <v>888</v>
+      </c>
+      <c r="J105" s="3" t="s">
+        <v>889</v>
+      </c>
+      <c r="K105" s="3">
+        <v>1</v>
+      </c>
+      <c r="L105" s="3" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" ht="56.25" x14ac:dyDescent="0.2">
+      <c r="A106" s="3" t="s">
+        <v>871</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>891</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>892</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>893</v>
+      </c>
+      <c r="F106" s="3" t="s">
+        <v>894</v>
+      </c>
+      <c r="G106" s="3" t="s">
+        <v>895</v>
+      </c>
+      <c r="H106" s="3" t="s">
+        <v>896</v>
+      </c>
+      <c r="I106" s="3" t="s">
+        <v>897</v>
+      </c>
+      <c r="J106" s="3" t="s">
+        <v>898</v>
+      </c>
+      <c r="K106" s="3">
+        <v>1</v>
+      </c>
+      <c r="L106" s="3" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12" ht="56.25" x14ac:dyDescent="0.2">
+      <c r="A107" s="3" t="s">
+        <v>871</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>901</v>
+      </c>
+      <c r="E107" s="3" t="s">
+        <v>902</v>
+      </c>
+      <c r="F107" s="3" t="s">
+        <v>903</v>
+      </c>
+      <c r="G107" s="3" t="s">
+        <v>904</v>
+      </c>
+      <c r="H107" s="3" t="s">
+        <v>905</v>
+      </c>
+      <c r="I107" s="3" t="s">
+        <v>906</v>
+      </c>
+      <c r="J107" s="3" t="s">
+        <v>907</v>
+      </c>
+      <c r="K107" s="3">
+        <v>1</v>
+      </c>
+      <c r="L107" s="3" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12" ht="56.25" x14ac:dyDescent="0.2">
+      <c r="A108" s="3" t="s">
+        <v>871</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>909</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>910</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>911</v>
+      </c>
+      <c r="E108" s="3" t="s">
+        <v>912</v>
+      </c>
+      <c r="F108" s="3" t="s">
+        <v>913</v>
+      </c>
+      <c r="G108" s="3" t="s">
+        <v>914</v>
+      </c>
+      <c r="H108" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="I108" s="3" t="s">
+        <v>916</v>
+      </c>
+      <c r="J108" s="3" t="s">
+        <v>917</v>
+      </c>
+      <c r="K108" s="3">
+        <v>1</v>
+      </c>
+      <c r="L108" s="3" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A109" s="3" t="s">
+        <v>871</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>909</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>919</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>920</v>
+      </c>
+      <c r="E109" s="3" t="s">
+        <v>921</v>
+      </c>
+      <c r="F109" s="3" t="s">
+        <v>922</v>
+      </c>
+      <c r="G109" s="3" t="s">
+        <v>923</v>
+      </c>
+      <c r="H109" s="3" t="s">
+        <v>924</v>
+      </c>
+      <c r="I109" s="3" t="s">
+        <v>925</v>
+      </c>
+      <c r="J109" s="3" t="s">
+        <v>926</v>
+      </c>
+      <c r="K109" s="3">
+        <v>1</v>
+      </c>
+      <c r="L109" s="3" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A110" s="3" t="s">
+        <v>871</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>909</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>928</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>929</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>930</v>
+      </c>
+      <c r="F110" s="3" t="s">
+        <v>931</v>
+      </c>
+      <c r="G110" s="3" t="s">
+        <v>932</v>
+      </c>
+      <c r="H110" s="3" t="s">
+        <v>933</v>
+      </c>
+      <c r="I110" s="3" t="s">
+        <v>934</v>
+      </c>
+      <c r="J110" s="3" t="s">
+        <v>935</v>
+      </c>
+      <c r="K110" s="3">
+        <v>1</v>
+      </c>
+      <c r="L110" s="3" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A111" s="3" t="s">
+        <v>871</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>909</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>937</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>938</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>939</v>
+      </c>
+      <c r="F111" s="3" t="s">
+        <v>940</v>
+      </c>
+      <c r="G111" s="3" t="s">
+        <v>941</v>
+      </c>
+      <c r="H111" s="3" t="s">
+        <v>942</v>
+      </c>
+      <c r="I111" s="3" t="s">
+        <v>943</v>
+      </c>
+      <c r="J111" s="3" t="s">
+        <v>944</v>
+      </c>
+      <c r="K111" s="3">
+        <v>1</v>
+      </c>
+      <c r="L111" s="3" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A112" s="3" t="s">
+        <v>871</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>909</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>946</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>947</v>
+      </c>
+      <c r="E112" s="3" t="s">
+        <v>948</v>
+      </c>
+      <c r="F112" s="3" t="s">
+        <v>949</v>
+      </c>
+      <c r="G112" s="3" t="s">
+        <v>950</v>
+      </c>
+      <c r="H112" s="3" t="s">
+        <v>951</v>
+      </c>
+      <c r="I112" s="3" t="s">
+        <v>952</v>
+      </c>
+      <c r="J112" s="3" t="s">
+        <v>953</v>
+      </c>
+      <c r="K112" s="3">
+        <v>1</v>
+      </c>
+      <c r="L112" s="3" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A113" s="3" t="s">
+        <v>871</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>955</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>956</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>957</v>
+      </c>
+      <c r="E113" s="3" t="s">
+        <v>958</v>
+      </c>
+      <c r="F113" s="3" t="s">
+        <v>959</v>
+      </c>
+      <c r="G113" s="3" t="s">
+        <v>960</v>
+      </c>
+      <c r="H113" s="3" t="s">
+        <v>961</v>
+      </c>
+      <c r="I113" s="3" t="s">
+        <v>962</v>
+      </c>
+      <c r="J113" s="3" t="s">
+        <v>963</v>
+      </c>
+      <c r="K113" s="3">
+        <v>1</v>
+      </c>
+      <c r="L113" s="3" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A114" s="3" t="s">
+        <v>871</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>955</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>966</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>967</v>
+      </c>
+      <c r="F114" s="3" t="s">
+        <v>968</v>
+      </c>
+      <c r="G114" s="3" t="s">
+        <v>969</v>
+      </c>
+      <c r="H114" s="3" t="s">
+        <v>970</v>
+      </c>
+      <c r="I114" s="3" t="s">
+        <v>971</v>
+      </c>
+      <c r="J114" s="3" t="s">
+        <v>972</v>
+      </c>
+      <c r="K114" s="3">
+        <v>1</v>
+      </c>
+      <c r="L114" s="3" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A115" s="3" t="s">
+        <v>871</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>974</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>975</v>
+      </c>
+      <c r="E115" s="3" t="s">
+        <v>976</v>
+      </c>
+      <c r="F115" s="3" t="s">
+        <v>977</v>
+      </c>
+      <c r="G115" s="3" t="s">
+        <v>978</v>
+      </c>
+      <c r="H115" s="3" t="s">
+        <v>979</v>
+      </c>
+      <c r="I115" s="3" t="s">
+        <v>813</v>
+      </c>
+      <c r="J115" s="3" t="s">
+        <v>980</v>
+      </c>
+      <c r="K115" s="3">
+        <v>1</v>
+      </c>
+      <c r="L115" s="3" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A116" s="3" t="s">
+        <v>871</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>982</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>983</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>984</v>
+      </c>
+      <c r="F116" s="3" t="s">
+        <v>985</v>
+      </c>
+      <c r="G116" s="3" t="s">
+        <v>986</v>
+      </c>
+      <c r="H116" s="3" t="s">
+        <v>987</v>
+      </c>
+      <c r="I116" s="3" t="s">
+        <v>988</v>
+      </c>
+      <c r="J116" s="3" t="s">
+        <v>989</v>
+      </c>
+      <c r="K116" s="3">
+        <v>1</v>
+      </c>
+      <c r="L116" s="3" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A117" s="3" t="s">
+        <v>871</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>991</v>
+      </c>
+      <c r="D117" s="3" t="s">
+        <v>992</v>
+      </c>
+      <c r="E117" s="3" t="s">
+        <v>993</v>
+      </c>
+      <c r="F117" s="3" t="s">
+        <v>994</v>
+      </c>
+      <c r="G117" s="3" t="s">
+        <v>995</v>
+      </c>
+      <c r="H117" s="3" t="s">
+        <v>996</v>
+      </c>
+      <c r="I117" s="3" t="s">
+        <v>997</v>
+      </c>
+      <c r="J117" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="K117" s="3">
+        <v>1</v>
+      </c>
+      <c r="L117" s="3" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A118" s="3" t="s">
+        <v>871</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>999</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>1000</v>
+      </c>
+      <c r="E118" s="3" t="s">
+        <v>1001</v>
+      </c>
+      <c r="F118" s="3" t="s">
+        <v>1002</v>
+      </c>
+      <c r="G118" s="3" t="s">
+        <v>1003</v>
+      </c>
+      <c r="H118" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="I118" s="3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="J118" s="3" t="s">
+        <v>1005</v>
+      </c>
+      <c r="K118" s="3">
+        <v>1</v>
+      </c>
+      <c r="L118" s="3" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A119" s="3" t="s">
+        <v>871</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>1008</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>1009</v>
+      </c>
+      <c r="E119" s="3" t="s">
+        <v>1010</v>
+      </c>
+      <c r="F119" s="3" t="s">
+        <v>1011</v>
+      </c>
+      <c r="G119" s="3" t="s">
+        <v>1012</v>
+      </c>
+      <c r="H119" s="3" t="s">
+        <v>1013</v>
+      </c>
+      <c r="I119" s="3" t="s">
+        <v>1014</v>
+      </c>
+      <c r="J119" s="3" t="s">
+        <v>1015</v>
+      </c>
+      <c r="K119" s="3">
+        <v>1</v>
+      </c>
+      <c r="L119" s="3" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A120" s="3" t="s">
+        <v>871</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>1017</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E120" s="3" t="s">
+        <v>1019</v>
+      </c>
+      <c r="F120" s="3" t="s">
+        <v>1020</v>
+      </c>
+      <c r="G120" s="3" t="s">
+        <v>1021</v>
+      </c>
+      <c r="H120" s="3" t="s">
+        <v>1022</v>
+      </c>
+      <c r="I120" s="3" t="s">
+        <v>1023</v>
+      </c>
+      <c r="J120" s="3" t="s">
+        <v>1024</v>
+      </c>
+      <c r="K120" s="3">
+        <v>1</v>
+      </c>
+      <c r="L120" s="3" t="s">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12" ht="56.25" x14ac:dyDescent="0.2">
+      <c r="A121" s="3" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>872</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>1027</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>1028</v>
+      </c>
+      <c r="E121" s="3" t="s">
+        <v>1029</v>
+      </c>
+      <c r="F121" s="3" t="s">
+        <v>1030</v>
+      </c>
+      <c r="G121" s="3" t="s">
+        <v>1031</v>
+      </c>
+      <c r="H121" s="3" t="s">
+        <v>1032</v>
+      </c>
+      <c r="I121" s="3" t="s">
+        <v>1033</v>
+      </c>
+      <c r="J121" s="3" t="s">
+        <v>1034</v>
+      </c>
+      <c r="K121" s="3">
+        <v>1</v>
+      </c>
+      <c r="L121" s="3" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A122" s="3" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>872</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>1037</v>
+      </c>
+      <c r="E122" s="3" t="s">
+        <v>1038</v>
+      </c>
+      <c r="F122" s="3" t="s">
+        <v>1039</v>
+      </c>
+      <c r="G122" s="3" t="s">
+        <v>1040</v>
+      </c>
+      <c r="H122" s="3" t="s">
+        <v>1041</v>
+      </c>
+      <c r="I122" s="3" t="s">
+        <v>1042</v>
+      </c>
+      <c r="J122" s="3" t="s">
+        <v>1043</v>
+      </c>
+      <c r="K122" s="3">
+        <v>1</v>
+      </c>
+      <c r="L122" s="3" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A123" s="3" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>1045</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>1046</v>
+      </c>
+      <c r="E123" s="3" t="s">
+        <v>1047</v>
+      </c>
+      <c r="F123" s="3" t="s">
+        <v>1048</v>
+      </c>
+      <c r="G123" s="3" t="s">
+        <v>1049</v>
+      </c>
+      <c r="H123" s="3" t="s">
+        <v>1050</v>
+      </c>
+      <c r="I123" s="3" t="s">
+        <v>1051</v>
+      </c>
+      <c r="J123" s="3" t="s">
+        <v>1052</v>
+      </c>
+      <c r="K123" s="3">
+        <v>1</v>
+      </c>
+      <c r="L123" s="3" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A124" s="3" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>1054</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>1055</v>
+      </c>
+      <c r="E124" s="3" t="s">
+        <v>1056</v>
+      </c>
+      <c r="F124" s="3" t="s">
+        <v>1057</v>
+      </c>
+      <c r="G124" s="3" t="s">
+        <v>904</v>
+      </c>
+      <c r="H124" s="3" t="s">
+        <v>905</v>
+      </c>
+      <c r="I124" s="3" t="s">
+        <v>1058</v>
+      </c>
+      <c r="J124" s="3" t="s">
+        <v>1059</v>
+      </c>
+      <c r="K124" s="3">
+        <v>1</v>
+      </c>
+      <c r="L124" s="3" t="s">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12" ht="33.75" x14ac:dyDescent="0.2">
+      <c r="A125" s="3" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>1062</v>
+      </c>
+      <c r="D125" s="3" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E125" s="3" t="s">
+        <v>1064</v>
+      </c>
+      <c r="F125" s="3" t="s">
+        <v>1065</v>
+      </c>
+      <c r="G125" s="3" t="s">
+        <v>1066</v>
+      </c>
+      <c r="H125" s="3" t="s">
+        <v>1067</v>
+      </c>
+      <c r="I125" s="3" t="s">
+        <v>1068</v>
+      </c>
+      <c r="J125" s="3" t="s">
+        <v>1069</v>
+      </c>
+      <c r="K125" s="3">
+        <v>1</v>
+      </c>
+      <c r="L125" s="3" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A126" s="3" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D126" s="3" t="s">
+        <v>1072</v>
+      </c>
+      <c r="E126" s="3" t="s">
+        <v>1073</v>
+      </c>
+      <c r="F126" s="3" t="s">
+        <v>1074</v>
+      </c>
+      <c r="G126" s="3" t="s">
+        <v>1075</v>
+      </c>
+      <c r="H126" s="3" t="s">
+        <v>1076</v>
+      </c>
+      <c r="I126" s="3" t="s">
+        <v>1077</v>
+      </c>
+      <c r="J126" s="3" t="s">
+        <v>1078</v>
+      </c>
+      <c r="K126" s="3">
+        <v>1</v>
+      </c>
+      <c r="L126" s="3" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="127" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A127" s="3" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C127" s="3" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D127" s="3" t="s">
+        <v>1082</v>
+      </c>
+      <c r="E127" s="3" t="s">
+        <v>1083</v>
+      </c>
+      <c r="F127" s="3" t="s">
+        <v>1084</v>
+      </c>
+      <c r="G127" s="3" t="s">
+        <v>1085</v>
+      </c>
+      <c r="H127" s="3" t="s">
+        <v>1086</v>
+      </c>
+      <c r="I127" s="3" t="s">
+        <v>1087</v>
+      </c>
+      <c r="J127" s="3" t="s">
+        <v>1088</v>
+      </c>
+      <c r="K127" s="3">
+        <v>1</v>
+      </c>
+      <c r="L127" s="3" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A128" s="3" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D128" s="3" t="s">
+        <v>1091</v>
+      </c>
+      <c r="E128" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="F128" s="3" t="s">
+        <v>1093</v>
+      </c>
+      <c r="G128" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H128" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="I128" s="3" t="s">
+        <v>1096</v>
+      </c>
+      <c r="J128" s="3" t="s">
+        <v>1097</v>
+      </c>
+      <c r="K128" s="3">
+        <v>1</v>
+      </c>
+      <c r="L128" s="3" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="129" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A129" s="3" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>1100</v>
+      </c>
+      <c r="D129" s="3" t="s">
+        <v>1101</v>
+      </c>
+      <c r="E129" s="3" t="s">
+        <v>1102</v>
+      </c>
+      <c r="F129" s="3" t="s">
+        <v>1103</v>
+      </c>
+      <c r="G129" s="3" t="s">
+        <v>1104</v>
+      </c>
+      <c r="H129" s="3" t="s">
+        <v>1105</v>
+      </c>
+      <c r="I129" s="3" t="s">
+        <v>1106</v>
+      </c>
+      <c r="J129" s="3" t="s">
+        <v>1107</v>
+      </c>
+      <c r="K129" s="3">
+        <v>1</v>
+      </c>
+      <c r="L129" s="3" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="130" spans="1:12" ht="33.75" x14ac:dyDescent="0.2">
+      <c r="A130" s="3" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C130" s="3" t="s">
+        <v>1109</v>
+      </c>
+      <c r="D130" s="3" t="s">
+        <v>1110</v>
+      </c>
+      <c r="E130" s="3" t="s">
+        <v>1111</v>
+      </c>
+      <c r="F130" s="3" t="s">
+        <v>1112</v>
+      </c>
+      <c r="G130" s="3" t="s">
+        <v>1113</v>
+      </c>
+      <c r="H130" s="3" t="s">
+        <v>805</v>
+      </c>
+      <c r="I130" s="3" t="s">
+        <v>1114</v>
+      </c>
+      <c r="J130" s="3" t="s">
+        <v>989</v>
+      </c>
+      <c r="K130" s="3">
+        <v>1</v>
+      </c>
+      <c r="L130" s="3" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="131" spans="1:12" ht="33.75" x14ac:dyDescent="0.2">
+      <c r="A131" s="3" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C131" s="3" t="s">
+        <v>1116</v>
+      </c>
+      <c r="D131" s="3" t="s">
+        <v>1117</v>
+      </c>
+      <c r="E131" s="3" t="s">
+        <v>1118</v>
+      </c>
+      <c r="F131" s="3" t="s">
+        <v>1119</v>
+      </c>
+      <c r="G131" s="3" t="s">
+        <v>1120</v>
+      </c>
+      <c r="H131" s="3" t="s">
+        <v>1121</v>
+      </c>
+      <c r="I131" s="3" t="s">
+        <v>1122</v>
+      </c>
+      <c r="J131" s="3" t="s">
+        <v>1123</v>
+      </c>
+      <c r="K131" s="3">
+        <v>1</v>
+      </c>
+      <c r="L131" s="3" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="132" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A132" s="3" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="C132" s="3" t="s">
+        <v>1125</v>
+      </c>
+      <c r="D132" s="3" t="s">
+        <v>1126</v>
+      </c>
+      <c r="E132" s="3" t="s">
+        <v>1127</v>
+      </c>
+      <c r="F132" s="3" t="s">
+        <v>1128</v>
+      </c>
+      <c r="G132" s="3" t="s">
+        <v>1129</v>
+      </c>
+      <c r="H132" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="I132" s="3" t="s">
+        <v>1130</v>
+      </c>
+      <c r="J132" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="K132" s="3">
+        <v>1</v>
+      </c>
+      <c r="L132" s="3" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="133" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A133" s="3" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B133" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="C133" s="3" t="s">
+        <v>1132</v>
+      </c>
+      <c r="D133" s="3" t="s">
+        <v>1133</v>
+      </c>
+      <c r="E133" s="3" t="s">
+        <v>1134</v>
+      </c>
+      <c r="F133" s="3" t="s">
+        <v>1135</v>
+      </c>
+      <c r="G133" s="3" t="s">
+        <v>1136</v>
+      </c>
+      <c r="H133" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="I133" s="3" t="s">
+        <v>1137</v>
+      </c>
+      <c r="J133" s="3" t="s">
+        <v>1138</v>
+      </c>
+      <c r="K133" s="3">
+        <v>1</v>
+      </c>
+      <c r="L133" s="3" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="134" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A134" s="3" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C134" s="3" t="s">
+        <v>1140</v>
+      </c>
+      <c r="D134" s="3" t="s">
+        <v>1141</v>
+      </c>
+      <c r="E134" s="3" t="s">
+        <v>1142</v>
+      </c>
+      <c r="F134" s="3" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G134" s="3" t="s">
+        <v>1144</v>
+      </c>
+      <c r="H134" s="3" t="s">
+        <v>1145</v>
+      </c>
+      <c r="I134" s="3" t="s">
+        <v>1146</v>
+      </c>
+      <c r="J134" s="3" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K134" s="3">
+        <v>1</v>
+      </c>
+      <c r="L134" s="3" t="s">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="135" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A135" s="3" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B135" s="3" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C135" s="3" t="s">
+        <v>1149</v>
+      </c>
+      <c r="D135" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="E135" s="3" t="s">
+        <v>1151</v>
+      </c>
+      <c r="F135" s="3" t="s">
+        <v>1152</v>
+      </c>
+      <c r="G135" s="3" t="s">
+        <v>1153</v>
+      </c>
+      <c r="H135" s="3" t="s">
+        <v>1154</v>
+      </c>
+      <c r="I135" s="3" t="s">
+        <v>1155</v>
+      </c>
+      <c r="J135" s="3" t="s">
+        <v>1156</v>
+      </c>
+      <c r="K135" s="3">
+        <v>1</v>
+      </c>
+      <c r="L135" s="3" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="136" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A136" s="3" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B136" s="3" t="s">
+        <v>872</v>
+      </c>
+      <c r="C136" s="3" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D136" s="3" t="s">
+        <v>1160</v>
+      </c>
+      <c r="E136" s="3" t="s">
+        <v>1161</v>
+      </c>
+      <c r="F136" s="3" t="s">
+        <v>1162</v>
+      </c>
+      <c r="G136" s="3" t="s">
+        <v>1163</v>
+      </c>
+      <c r="H136" s="3" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I136" s="3" t="s">
+        <v>1165</v>
+      </c>
+      <c r="J136" s="3" t="s">
+        <v>1166</v>
+      </c>
+      <c r="K136" s="3">
+        <v>1</v>
+      </c>
+      <c r="L136" s="3" t="s">
+        <v>1167</v>
+      </c>
+    </row>
+    <row r="137" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A137" s="3" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>872</v>
+      </c>
+      <c r="C137" s="3" t="s">
+        <v>1168</v>
+      </c>
+      <c r="D137" s="3" t="s">
+        <v>1169</v>
+      </c>
+      <c r="E137" s="3" t="s">
+        <v>1170</v>
+      </c>
+      <c r="F137" s="3" t="s">
+        <v>1171</v>
+      </c>
+      <c r="G137" s="3" t="s">
+        <v>1172</v>
+      </c>
+      <c r="H137" s="3" t="s">
+        <v>1173</v>
+      </c>
+      <c r="I137" s="3" t="s">
+        <v>1174</v>
+      </c>
+      <c r="J137" s="3" t="s">
+        <v>1175</v>
+      </c>
+      <c r="K137" s="3">
+        <v>1</v>
+      </c>
+      <c r="L137" s="3" t="s">
+        <v>1176</v>
+      </c>
+    </row>
+    <row r="138" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A138" s="3" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B138" s="3" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C138" s="3" t="s">
+        <v>1178</v>
+      </c>
+      <c r="D138" s="3" t="s">
+        <v>1179</v>
+      </c>
+      <c r="E138" s="3" t="s">
+        <v>1180</v>
+      </c>
+      <c r="F138" s="3" t="s">
+        <v>1181</v>
+      </c>
+      <c r="G138" s="3" t="s">
+        <v>1182</v>
+      </c>
+      <c r="H138" s="3" t="s">
+        <v>1183</v>
+      </c>
+      <c r="I138" s="3" t="s">
+        <v>1184</v>
+      </c>
+      <c r="J138" s="3" t="s">
+        <v>1185</v>
+      </c>
+      <c r="K138" s="3">
+        <v>1</v>
+      </c>
+      <c r="L138" s="3" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="139" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A139" s="3" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B139" s="3" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C139" s="3" t="s">
+        <v>1187</v>
+      </c>
+      <c r="D139" s="3" t="s">
+        <v>1188</v>
+      </c>
+      <c r="E139" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="F139" s="3" t="s">
+        <v>1190</v>
+      </c>
+      <c r="G139" s="3" t="s">
+        <v>1191</v>
+      </c>
+      <c r="H139" s="3" t="s">
+        <v>1192</v>
+      </c>
+      <c r="I139" s="3" t="s">
+        <v>1193</v>
+      </c>
+      <c r="J139" s="3" t="s">
+        <v>1194</v>
+      </c>
+      <c r="K139" s="3">
+        <v>1</v>
+      </c>
+      <c r="L139" s="3" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="140" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A140" s="3" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B140" s="3" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C140" s="3" t="s">
+        <v>1196</v>
+      </c>
+      <c r="D140" s="3" t="s">
+        <v>1197</v>
+      </c>
+      <c r="E140" s="3" t="s">
+        <v>1198</v>
+      </c>
+      <c r="F140" s="3" t="s">
+        <v>1199</v>
+      </c>
+      <c r="G140" s="3" t="s">
+        <v>1200</v>
+      </c>
+      <c r="H140" s="3" t="s">
+        <v>1201</v>
+      </c>
+      <c r="I140" s="3" t="s">
+        <v>1202</v>
+      </c>
+      <c r="J140" s="3" t="s">
+        <v>1203</v>
+      </c>
+      <c r="K140" s="3">
+        <v>1</v>
+      </c>
+      <c r="L140" s="3" t="s">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="141" spans="1:12" ht="67.5" x14ac:dyDescent="0.2">
+      <c r="A141" s="3" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B141" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="C141" s="3" t="s">
+        <v>1205</v>
+      </c>
+      <c r="D141" s="3" t="s">
+        <v>1206</v>
+      </c>
+      <c r="E141" s="3" t="s">
+        <v>1207</v>
+      </c>
+      <c r="F141" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="G141" s="3" t="s">
+        <v>1209</v>
+      </c>
+      <c r="H141" s="3" t="s">
+        <v>1210</v>
+      </c>
+      <c r="I141" s="3" t="s">
+        <v>1211</v>
+      </c>
+      <c r="J141" s="3" t="s">
+        <v>1212</v>
+      </c>
+      <c r="K141" s="3">
+        <v>1</v>
+      </c>
+      <c r="L141" s="3" t="s">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="142" spans="1:12" ht="33.75" x14ac:dyDescent="0.2">
+      <c r="A142" s="3" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B142" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="C142" s="3" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D142" s="3" t="s">
+        <v>1215</v>
+      </c>
+      <c r="E142" s="3" t="s">
+        <v>1216</v>
+      </c>
+      <c r="F142" s="3" t="s">
+        <v>1217</v>
+      </c>
+      <c r="G142" s="3" t="s">
+        <v>1218</v>
+      </c>
+      <c r="H142" s="3" t="s">
+        <v>1219</v>
+      </c>
+      <c r="I142" s="3" t="s">
+        <v>1023</v>
+      </c>
+      <c r="J142" s="3" t="s">
+        <v>1024</v>
+      </c>
+      <c r="K142" s="3">
+        <v>1</v>
+      </c>
+      <c r="L142" s="3" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="143" spans="1:12" ht="56.25" x14ac:dyDescent="0.2">
+      <c r="A143" s="3" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B143" s="3" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C143" s="3" t="s">
+        <v>1222</v>
+      </c>
+      <c r="D143" s="3" t="s">
+        <v>1223</v>
+      </c>
+      <c r="E143" s="3" t="s">
+        <v>1224</v>
+      </c>
+      <c r="F143" s="3" t="s">
+        <v>1225</v>
+      </c>
+      <c r="G143" s="3" t="s">
+        <v>1226</v>
+      </c>
+      <c r="H143" s="3" t="s">
+        <v>1227</v>
+      </c>
+      <c r="I143" s="3" t="s">
+        <v>1228</v>
+      </c>
+      <c r="J143" s="3" t="s">
+        <v>1229</v>
+      </c>
+      <c r="K143" s="3">
+        <v>1</v>
+      </c>
+      <c r="L143" s="3" t="s">
+        <v>1176</v>
+      </c>
+    </row>
+    <row r="144" spans="1:12" ht="67.5" x14ac:dyDescent="0.2">
+      <c r="A144" s="3" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B144" s="3" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C144" s="3" t="s">
+        <v>1230</v>
+      </c>
+      <c r="D144" s="3" t="s">
+        <v>1231</v>
+      </c>
+      <c r="E144" s="3" t="s">
+        <v>1232</v>
+      </c>
+      <c r="F144" s="3" t="s">
+        <v>1233</v>
+      </c>
+      <c r="G144" s="3" t="s">
+        <v>1234</v>
+      </c>
+      <c r="H144" s="3" t="s">
+        <v>1235</v>
+      </c>
+      <c r="I144" s="3" t="s">
+        <v>1236</v>
+      </c>
+      <c r="J144" s="3" t="s">
+        <v>1237</v>
+      </c>
+      <c r="K144" s="3">
+        <v>1</v>
+      </c>
+      <c r="L144" s="3" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="145" spans="1:12" ht="33.75" x14ac:dyDescent="0.2">
+      <c r="A145" s="3" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B145" s="3" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C145" s="3" t="s">
+        <v>1240</v>
+      </c>
+      <c r="D145" s="3" t="s">
+        <v>1241</v>
+      </c>
+      <c r="E145" s="3" t="s">
+        <v>1242</v>
+      </c>
+      <c r="F145" s="3" t="s">
+        <v>1243</v>
+      </c>
+      <c r="G145" s="3" t="s">
+        <v>1244</v>
+      </c>
+      <c r="H145" s="3" t="s">
+        <v>1245</v>
+      </c>
+      <c r="I145" s="3" t="s">
+        <v>1246</v>
+      </c>
+      <c r="J145" s="3" t="s">
+        <v>1247</v>
+      </c>
+      <c r="K145" s="3">
+        <v>1</v>
+      </c>
+      <c r="L145" s="3" t="s">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="146" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A146" s="3" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B146" s="3" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C146" s="3" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D146" s="3" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E146" s="3" t="s">
+        <v>1251</v>
+      </c>
+      <c r="F146" s="3" t="s">
+        <v>1252</v>
+      </c>
+      <c r="G146" s="3" t="s">
+        <v>1253</v>
+      </c>
+      <c r="H146" s="3" t="s">
+        <v>1254</v>
+      </c>
+      <c r="I146" s="3" t="s">
+        <v>1255</v>
+      </c>
+      <c r="J146" s="3" t="s">
+        <v>1256</v>
+      </c>
+      <c r="K146" s="3">
+        <v>1</v>
+      </c>
+      <c r="L146" s="3" t="s">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="147" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A147" s="3" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B147" s="3" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C147" s="3" t="s">
+        <v>1259</v>
+      </c>
+      <c r="D147" s="3" t="s">
+        <v>1260</v>
+      </c>
+      <c r="E147" s="3" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F147" s="3" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G147" s="3" t="s">
+        <v>1263</v>
+      </c>
+      <c r="H147" s="3" t="s">
+        <v>1264</v>
+      </c>
+      <c r="I147" s="3" t="s">
+        <v>1265</v>
+      </c>
+      <c r="J147" s="3" t="s">
+        <v>1266</v>
+      </c>
+      <c r="K147" s="3">
+        <v>1</v>
+      </c>
+      <c r="L147" s="3" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="148" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A148" s="3" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B148" s="3" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C148" s="3" t="s">
+        <v>1268</v>
+      </c>
+      <c r="D148" s="3" t="s">
+        <v>1269</v>
+      </c>
+      <c r="E148" s="3" t="s">
+        <v>1270</v>
+      </c>
+      <c r="F148" s="3" t="s">
+        <v>1271</v>
+      </c>
+      <c r="G148" s="3" t="s">
+        <v>1272</v>
+      </c>
+      <c r="H148" s="3" t="s">
+        <v>1273</v>
+      </c>
+      <c r="I148" s="3" t="s">
+        <v>1274</v>
+      </c>
+      <c r="J148" s="3" t="s">
+        <v>1275</v>
+      </c>
+      <c r="K148" s="3">
+        <v>1</v>
+      </c>
+      <c r="L148" s="3" t="s">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="149" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A149" s="3" t="s">
+        <v>1277</v>
+      </c>
+      <c r="B149" s="3" t="s">
+        <v>872</v>
+      </c>
+      <c r="C149" s="3" t="s">
+        <v>1278</v>
+      </c>
+      <c r="D149" s="3" t="s">
+        <v>1279</v>
+      </c>
+      <c r="E149" s="3" t="s">
+        <v>1280</v>
+      </c>
+      <c r="F149" s="3" t="s">
+        <v>1281</v>
+      </c>
+      <c r="G149" s="3" t="s">
+        <v>1282</v>
+      </c>
+      <c r="H149" s="3" t="s">
+        <v>1283</v>
+      </c>
+      <c r="I149" s="3" t="s">
+        <v>1284</v>
+      </c>
+      <c r="J149" s="3" t="s">
+        <v>1285</v>
+      </c>
+      <c r="K149" s="3">
+        <v>1</v>
+      </c>
+      <c r="L149" s="3" t="s">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="150" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A150" s="3" t="s">
+        <v>1277</v>
+      </c>
+      <c r="B150" s="3" t="s">
+        <v>872</v>
+      </c>
+      <c r="C150" s="3" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D150" s="3" t="s">
+        <v>1288</v>
+      </c>
+      <c r="E150" s="3" t="s">
+        <v>1289</v>
+      </c>
+      <c r="F150" s="3" t="s">
+        <v>1290</v>
+      </c>
+      <c r="G150" s="3" t="s">
+        <v>1291</v>
+      </c>
+      <c r="H150" s="3" t="s">
+        <v>1292</v>
+      </c>
+      <c r="I150" s="3" t="s">
+        <v>1293</v>
+      </c>
+      <c r="J150" s="3" t="s">
+        <v>1294</v>
+      </c>
+      <c r="K150" s="3">
+        <v>1</v>
+      </c>
+      <c r="L150" s="3" t="s">
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="151" spans="1:12" ht="33.75" x14ac:dyDescent="0.2">
+      <c r="A151" s="3" t="s">
+        <v>1277</v>
+      </c>
+      <c r="B151" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="C151" s="3" t="s">
+        <v>1296</v>
+      </c>
+      <c r="D151" s="3" t="s">
+        <v>1297</v>
+      </c>
+      <c r="E151" s="3" t="s">
+        <v>1298</v>
+      </c>
+      <c r="F151" s="3" t="s">
+        <v>1299</v>
+      </c>
+      <c r="G151" s="3" t="s">
+        <v>1300</v>
+      </c>
+      <c r="H151" s="3" t="s">
+        <v>1301</v>
+      </c>
+      <c r="I151" s="3" t="s">
+        <v>662</v>
+      </c>
+      <c r="J151" s="3" t="s">
+        <v>1302</v>
+      </c>
+      <c r="K151" s="3">
+        <v>1</v>
+      </c>
+      <c r="L151" s="3" t="s">
+        <v>1303</v>
+      </c>
+    </row>
+    <row r="152" spans="1:12" ht="56.25" x14ac:dyDescent="0.2">
+      <c r="A152" s="3" t="s">
+        <v>1277</v>
+      </c>
+      <c r="B152" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="C152" s="3" t="s">
+        <v>1304</v>
+      </c>
+      <c r="D152" s="3" t="s">
+        <v>1305</v>
+      </c>
+      <c r="E152" s="3" t="s">
+        <v>1306</v>
+      </c>
+      <c r="F152" s="3" t="s">
+        <v>1307</v>
+      </c>
+      <c r="G152" s="3" t="s">
+        <v>1308</v>
+      </c>
+      <c r="H152" s="3" t="s">
+        <v>1309</v>
+      </c>
+      <c r="I152" s="3" t="s">
+        <v>1310</v>
+      </c>
+      <c r="J152" s="3" t="s">
+        <v>1311</v>
+      </c>
+      <c r="K152" s="3">
+        <v>1</v>
+      </c>
+      <c r="L152" s="3" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="153" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A153" s="3" t="s">
+        <v>1277</v>
+      </c>
+      <c r="B153" s="3" t="s">
+        <v>1313</v>
+      </c>
+      <c r="C153" s="3" t="s">
+        <v>1314</v>
+      </c>
+      <c r="D153" s="3" t="s">
+        <v>1315</v>
+      </c>
+      <c r="E153" s="3" t="s">
+        <v>1316</v>
+      </c>
+      <c r="F153" s="3" t="s">
+        <v>1317</v>
+      </c>
+      <c r="G153" s="3" t="s">
+        <v>1318</v>
+      </c>
+      <c r="H153" s="3" t="s">
+        <v>1319</v>
+      </c>
+      <c r="I153" s="3" t="s">
+        <v>1320</v>
+      </c>
+      <c r="J153" s="3" t="s">
+        <v>1321</v>
+      </c>
+      <c r="K153" s="3">
+        <v>1</v>
+      </c>
+      <c r="L153" s="3" t="s">
+        <v>1322</v>
+      </c>
+    </row>
+    <row r="154" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A154" s="3" t="s">
+        <v>1277</v>
+      </c>
+      <c r="B154" s="3" t="s">
+        <v>1313</v>
+      </c>
+      <c r="C154" s="3" t="s">
+        <v>1323</v>
+      </c>
+      <c r="D154" s="3" t="s">
+        <v>1324</v>
+      </c>
+      <c r="E154" s="3" t="s">
+        <v>1325</v>
+      </c>
+      <c r="F154" s="3" t="s">
+        <v>1326</v>
+      </c>
+      <c r="G154" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="H154" s="3" t="s">
+        <v>1327</v>
+      </c>
+      <c r="I154" s="3" t="s">
+        <v>1328</v>
+      </c>
+      <c r="J154" s="3" t="s">
+        <v>1329</v>
+      </c>
+      <c r="K154" s="3">
+        <v>1</v>
+      </c>
+      <c r="L154" s="3" t="s">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="155" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A155" s="3" t="s">
+        <v>1277</v>
+      </c>
+      <c r="B155" s="3" t="s">
+        <v>1331</v>
+      </c>
+      <c r="C155" s="3" t="s">
+        <v>1332</v>
+      </c>
+      <c r="D155" s="3" t="s">
+        <v>1333</v>
+      </c>
+      <c r="E155" s="3" t="s">
+        <v>1334</v>
+      </c>
+      <c r="F155" s="3" t="s">
+        <v>1335</v>
+      </c>
+      <c r="G155" s="3" t="s">
+        <v>1336</v>
+      </c>
+      <c r="H155" s="3" t="s">
+        <v>1337</v>
+      </c>
+      <c r="I155" s="3" t="s">
+        <v>1338</v>
+      </c>
+      <c r="J155" s="3" t="s">
+        <v>1339</v>
+      </c>
+      <c r="K155" s="3">
+        <v>1</v>
+      </c>
+      <c r="L155" s="3" t="s">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="156" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A156" s="3" t="s">
+        <v>1277</v>
+      </c>
+      <c r="B156" s="3" t="s">
+        <v>1331</v>
+      </c>
+      <c r="C156" s="3" t="s">
+        <v>1341</v>
+      </c>
+      <c r="D156" s="3" t="s">
+        <v>1342</v>
+      </c>
+      <c r="E156" s="3" t="s">
+        <v>1343</v>
+      </c>
+      <c r="F156" s="3" t="s">
+        <v>1344</v>
+      </c>
+      <c r="G156" s="3" t="s">
+        <v>1345</v>
+      </c>
+      <c r="H156" s="3" t="s">
+        <v>1346</v>
+      </c>
+      <c r="I156" s="3" t="s">
+        <v>1347</v>
+      </c>
+      <c r="J156" s="3" t="s">
+        <v>1348</v>
+      </c>
+      <c r="K156" s="3">
+        <v>1</v>
+      </c>
+      <c r="L156" s="3" t="s">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="157" spans="1:12" ht="33.75" x14ac:dyDescent="0.2">
+      <c r="A157" s="3" t="s">
+        <v>1277</v>
+      </c>
+      <c r="B157" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="C157" s="3" t="s">
+        <v>1349</v>
+      </c>
+      <c r="D157" s="3" t="s">
+        <v>1350</v>
+      </c>
+      <c r="E157" s="3" t="s">
+        <v>1351</v>
+      </c>
+      <c r="F157" s="3" t="s">
+        <v>1352</v>
+      </c>
+      <c r="G157" s="3" t="s">
+        <v>1353</v>
+      </c>
+      <c r="H157" s="3" t="s">
+        <v>1354</v>
+      </c>
+      <c r="I157" s="3" t="s">
+        <v>739</v>
+      </c>
+      <c r="J157" s="3" t="s">
+        <v>1355</v>
+      </c>
+      <c r="K157" s="3">
+        <v>1</v>
+      </c>
+      <c r="L157" s="3" t="s">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="158" spans="1:12" ht="33.75" x14ac:dyDescent="0.2">
+      <c r="A158" s="3" t="s">
+        <v>1277</v>
+      </c>
+      <c r="B158" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="C158" s="3" t="s">
+        <v>1357</v>
+      </c>
+      <c r="D158" s="3" t="s">
+        <v>1358</v>
+      </c>
+      <c r="E158" s="3" t="s">
+        <v>1359</v>
+      </c>
+      <c r="F158" s="3" t="s">
+        <v>1360</v>
+      </c>
+      <c r="G158" s="3" t="s">
+        <v>1361</v>
+      </c>
+      <c r="H158" s="3" t="s">
+        <v>1362</v>
+      </c>
+      <c r="I158" s="3" t="s">
+        <v>1363</v>
+      </c>
+      <c r="J158" s="3" t="s">
+        <v>1364</v>
+      </c>
+      <c r="K158" s="3">
+        <v>1</v>
+      </c>
+      <c r="L158" s="3" t="s">
+        <v>1365</v>
+      </c>
+    </row>
+    <row r="159" spans="1:12" ht="33.75" x14ac:dyDescent="0.2">
+      <c r="A159" s="3" t="s">
+        <v>1277</v>
+      </c>
+      <c r="B159" s="3" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C159" s="3" t="s">
+        <v>1367</v>
+      </c>
+      <c r="D159" s="3" t="s">
+        <v>1368</v>
+      </c>
+      <c r="E159" s="3" t="s">
+        <v>1369</v>
+      </c>
+      <c r="F159" s="3" t="s">
+        <v>1370</v>
+      </c>
+      <c r="G159" s="3" t="s">
+        <v>1371</v>
+      </c>
+      <c r="H159" s="3" t="s">
+        <v>1372</v>
+      </c>
+      <c r="I159" s="3" t="s">
+        <v>1373</v>
+      </c>
+      <c r="J159" s="3" t="s">
+        <v>1374</v>
+      </c>
+      <c r="K159" s="3">
+        <v>1</v>
+      </c>
+      <c r="L159" s="3" t="s">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="160" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A160" s="3" t="s">
+        <v>1277</v>
+      </c>
+      <c r="B160" s="3" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C160" s="3" t="s">
+        <v>1376</v>
+      </c>
+      <c r="D160" s="3" t="s">
+        <v>1377</v>
+      </c>
+      <c r="E160" s="3" t="s">
+        <v>1378</v>
+      </c>
+      <c r="F160" s="3" t="s">
+        <v>1379</v>
+      </c>
+      <c r="G160" s="3" t="s">
+        <v>1380</v>
+      </c>
+      <c r="H160" s="3" t="s">
+        <v>1381</v>
+      </c>
+      <c r="I160" s="3" t="s">
+        <v>1382</v>
+      </c>
+      <c r="J160" s="3" t="s">
+        <v>1383</v>
+      </c>
+      <c r="K160" s="3">
+        <v>1</v>
+      </c>
+      <c r="L160" s="3" t="s">
+        <v>1384</v>
+      </c>
+    </row>
+    <row r="161" spans="1:12" ht="56.25" x14ac:dyDescent="0.2">
+      <c r="A161" s="3" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B161" s="3" t="s">
+        <v>872</v>
+      </c>
+      <c r="C161" s="3" t="s">
+        <v>1386</v>
+      </c>
+      <c r="D161" s="3" t="s">
+        <v>1387</v>
+      </c>
+      <c r="E161" s="3" t="s">
+        <v>1388</v>
+      </c>
+      <c r="F161" s="3" t="s">
+        <v>1389</v>
+      </c>
+      <c r="G161" s="3" t="s">
+        <v>1390</v>
+      </c>
+      <c r="H161" s="3" t="s">
+        <v>1391</v>
+      </c>
+      <c r="I161" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="J161" s="3" t="s">
+        <v>1393</v>
+      </c>
+      <c r="K161" s="3">
+        <v>1</v>
+      </c>
+      <c r="L161" s="3" t="s">
+        <v>1394</v>
+      </c>
+    </row>
+    <row r="162" spans="1:12" ht="56.25" x14ac:dyDescent="0.2">
+      <c r="A162" s="3" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B162" s="3" t="s">
+        <v>872</v>
+      </c>
+      <c r="C162" s="3" t="s">
+        <v>1395</v>
+      </c>
+      <c r="D162" s="3" t="s">
+        <v>1396</v>
+      </c>
+      <c r="E162" s="3" t="s">
+        <v>1397</v>
+      </c>
+      <c r="F162" s="3" t="s">
+        <v>1398</v>
+      </c>
+      <c r="G162" s="3" t="s">
+        <v>1399</v>
+      </c>
+      <c r="H162" s="3" t="s">
+        <v>1400</v>
+      </c>
+      <c r="I162" s="3" t="s">
+        <v>1401</v>
+      </c>
+      <c r="J162" s="3" t="s">
+        <v>1402</v>
+      </c>
+      <c r="K162" s="3">
+        <v>1</v>
+      </c>
+      <c r="L162" s="3" t="s">
+        <v>1403</v>
+      </c>
+    </row>
+    <row r="163" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A163" s="3" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B163" s="3" t="s">
+        <v>1404</v>
+      </c>
+      <c r="C163" s="3" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D163" s="3" t="s">
+        <v>1406</v>
+      </c>
+      <c r="E163" s="3" t="s">
+        <v>1407</v>
+      </c>
+      <c r="F163" s="3" t="s">
+        <v>1408</v>
+      </c>
+      <c r="G163" s="3" t="s">
+        <v>1409</v>
+      </c>
+      <c r="H163" s="3" t="s">
+        <v>1410</v>
+      </c>
+      <c r="I163" s="3" t="s">
+        <v>1411</v>
+      </c>
+      <c r="J163" s="3" t="s">
+        <v>1412</v>
+      </c>
+      <c r="K163" s="3">
+        <v>1</v>
+      </c>
+      <c r="L163" s="3" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="164" spans="1:12" ht="33.75" x14ac:dyDescent="0.2">
+      <c r="A164" s="3" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B164" s="3" t="s">
+        <v>1404</v>
+      </c>
+      <c r="C164" s="3" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D164" s="3" t="s">
+        <v>1415</v>
+      </c>
+      <c r="E164" s="3" t="s">
+        <v>1416</v>
+      </c>
+      <c r="F164" s="3" t="s">
+        <v>1417</v>
+      </c>
+      <c r="G164" s="3" t="s">
+        <v>1418</v>
+      </c>
+      <c r="H164" s="3" t="s">
+        <v>1419</v>
+      </c>
+      <c r="I164" s="3" t="s">
+        <v>1420</v>
+      </c>
+      <c r="J164" s="3" t="s">
+        <v>1421</v>
+      </c>
+      <c r="K164" s="3">
+        <v>1</v>
+      </c>
+      <c r="L164" s="3" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="165" spans="1:12" ht="33.75" x14ac:dyDescent="0.2">
+      <c r="A165" s="3" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B165" s="3" t="s">
+        <v>1423</v>
+      </c>
+      <c r="C165" s="3" t="s">
+        <v>1424</v>
+      </c>
+      <c r="D165" s="3" t="s">
+        <v>1425</v>
+      </c>
+      <c r="E165" s="3" t="s">
+        <v>1426</v>
+      </c>
+      <c r="F165" s="3" t="s">
+        <v>1427</v>
+      </c>
+      <c r="G165" s="3" t="s">
+        <v>1428</v>
+      </c>
+      <c r="H165" s="3" t="s">
+        <v>1429</v>
+      </c>
+      <c r="I165" s="3" t="s">
+        <v>1430</v>
+      </c>
+      <c r="J165" s="3" t="s">
+        <v>1431</v>
+      </c>
+      <c r="K165" s="3">
+        <v>1</v>
+      </c>
+      <c r="L165" s="3" t="s">
+        <v>1432</v>
+      </c>
+    </row>
+    <row r="166" spans="1:12" ht="33.75" x14ac:dyDescent="0.2">
+      <c r="A166" s="3" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B166" s="3" t="s">
+        <v>1423</v>
+      </c>
+      <c r="C166" s="3" t="s">
+        <v>1433</v>
+      </c>
+      <c r="D166" s="3" t="s">
+        <v>1434</v>
+      </c>
+      <c r="E166" s="3" t="s">
+        <v>1435</v>
+      </c>
+      <c r="F166" s="3" t="s">
+        <v>1436</v>
+      </c>
+      <c r="G166" s="3" t="s">
+        <v>1437</v>
+      </c>
+      <c r="H166" s="3" t="s">
+        <v>1381</v>
+      </c>
+      <c r="I166" s="3" t="s">
+        <v>1438</v>
+      </c>
+      <c r="J166" s="3" t="s">
+        <v>1439</v>
+      </c>
+      <c r="K166" s="3">
+        <v>1</v>
+      </c>
+      <c r="L166" s="3" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="167" spans="1:12" ht="67.5" x14ac:dyDescent="0.2">
+      <c r="A167" s="3" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B167" s="3" t="s">
+        <v>1441</v>
+      </c>
+      <c r="C167" s="3" t="s">
+        <v>1442</v>
+      </c>
+      <c r="D167" s="3" t="s">
+        <v>1443</v>
+      </c>
+      <c r="E167" s="3" t="s">
+        <v>1444</v>
+      </c>
+      <c r="F167" s="3" t="s">
+        <v>1445</v>
+      </c>
+      <c r="G167" s="3" t="s">
+        <v>1446</v>
+      </c>
+      <c r="H167" s="3" t="s">
+        <v>1447</v>
+      </c>
+      <c r="I167" s="3" t="s">
+        <v>1448</v>
+      </c>
+      <c r="J167" s="3" t="s">
+        <v>1449</v>
+      </c>
+      <c r="K167" s="3">
+        <v>1</v>
+      </c>
+      <c r="L167" s="3" t="s">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="168" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A168" s="3" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B168" s="3" t="s">
+        <v>1441</v>
+      </c>
+      <c r="C168" s="3" t="s">
+        <v>1451</v>
+      </c>
+      <c r="D168" s="3" t="s">
+        <v>1452</v>
+      </c>
+      <c r="E168" s="3" t="s">
+        <v>1453</v>
+      </c>
+      <c r="F168" s="3" t="s">
+        <v>1454</v>
+      </c>
+      <c r="G168" s="3" t="s">
+        <v>1455</v>
+      </c>
+      <c r="H168" s="3" t="s">
+        <v>1456</v>
+      </c>
+      <c r="I168" s="3" t="s">
+        <v>1457</v>
+      </c>
+      <c r="J168" s="3" t="s">
+        <v>1458</v>
+      </c>
+      <c r="K168" s="3">
+        <v>1</v>
+      </c>
+      <c r="L168" s="3" t="s">
+        <v>1459</v>
+      </c>
+    </row>
+    <row r="169" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A169" s="3" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B169" s="3" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C169" s="3" t="s">
+        <v>1460</v>
+      </c>
+      <c r="D169" s="3" t="s">
+        <v>1461</v>
+      </c>
+      <c r="E169" s="3" t="s">
+        <v>1462</v>
+      </c>
+      <c r="F169" s="3" t="s">
+        <v>1463</v>
+      </c>
+      <c r="G169" s="3" t="s">
+        <v>1464</v>
+      </c>
+      <c r="H169" s="3" t="s">
+        <v>1465</v>
+      </c>
+      <c r="I169" s="3" t="s">
+        <v>1466</v>
+      </c>
+      <c r="J169" s="3" t="s">
+        <v>1229</v>
+      </c>
+      <c r="K169" s="3">
+        <v>1</v>
+      </c>
+      <c r="L169" s="3" t="s">
+        <v>1467</v>
+      </c>
+    </row>
+    <row r="170" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A170" s="3" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B170" s="3" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C170" s="3" t="s">
+        <v>1468</v>
+      </c>
+      <c r="D170" s="3" t="s">
+        <v>1469</v>
+      </c>
+      <c r="E170" s="3" t="s">
+        <v>1470</v>
+      </c>
+      <c r="F170" s="3" t="s">
+        <v>1471</v>
+      </c>
+      <c r="G170" s="3" t="s">
+        <v>1472</v>
+      </c>
+      <c r="H170" s="3" t="s">
+        <v>1473</v>
+      </c>
+      <c r="I170" s="3" t="s">
+        <v>1474</v>
+      </c>
+      <c r="J170" s="3" t="s">
+        <v>1475</v>
+      </c>
+      <c r="K170" s="3">
+        <v>1</v>
+      </c>
+      <c r="L170" s="3" t="s">
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="171" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A171" s="3" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B171" s="3" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C171" s="3" t="s">
+        <v>1477</v>
+      </c>
+      <c r="D171" s="3" t="s">
+        <v>1478</v>
+      </c>
+      <c r="E171" s="3" t="s">
+        <v>1479</v>
+      </c>
+      <c r="F171" s="3" t="s">
+        <v>1480</v>
+      </c>
+      <c r="G171" s="3" t="s">
+        <v>1481</v>
+      </c>
+      <c r="H171" s="3" t="s">
+        <v>1482</v>
+      </c>
+      <c r="I171" s="3" t="s">
+        <v>1483</v>
+      </c>
+      <c r="J171" s="3" t="s">
+        <v>1484</v>
+      </c>
+      <c r="K171" s="3">
+        <v>1</v>
+      </c>
+      <c r="L171" s="3" t="s">
+        <v>1485</v>
+      </c>
+    </row>
+    <row r="172" spans="1:12" ht="33.75" x14ac:dyDescent="0.2">
+      <c r="A172" s="3" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B172" s="3" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C172" s="3" t="s">
+        <v>1486</v>
+      </c>
+      <c r="D172" s="3" t="s">
+        <v>1487</v>
+      </c>
+      <c r="E172" s="3" t="s">
+        <v>1488</v>
+      </c>
+      <c r="F172" s="3" t="s">
+        <v>1489</v>
+      </c>
+      <c r="G172" s="3" t="s">
+        <v>1490</v>
+      </c>
+      <c r="H172" s="3" t="s">
+        <v>1491</v>
+      </c>
+      <c r="I172" s="3" t="s">
+        <v>1492</v>
+      </c>
+      <c r="J172" s="3" t="s">
+        <v>1493</v>
+      </c>
+      <c r="K172" s="3">
+        <v>1</v>
+      </c>
+      <c r="L172" s="3" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="173" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A173" s="3" t="s">
+        <v>1495</v>
+      </c>
+      <c r="B173" s="3" t="s">
+        <v>872</v>
+      </c>
+      <c r="C173" s="3" t="s">
+        <v>1496</v>
+      </c>
+      <c r="D173" s="3" t="s">
+        <v>1497</v>
+      </c>
+      <c r="E173" s="3" t="s">
+        <v>1498</v>
+      </c>
+      <c r="F173" s="3" t="s">
+        <v>1499</v>
+      </c>
+      <c r="G173" s="3" t="s">
+        <v>1500</v>
+      </c>
+      <c r="H173" s="3" t="s">
+        <v>1501</v>
+      </c>
+      <c r="I173" s="3" t="s">
+        <v>1502</v>
+      </c>
+      <c r="J173" s="3" t="s">
+        <v>1503</v>
+      </c>
+      <c r="K173" s="3">
+        <v>1</v>
+      </c>
+      <c r="L173" s="3" t="s">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="174" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A174" s="3" t="s">
+        <v>1495</v>
+      </c>
+      <c r="B174" s="3" t="s">
+        <v>872</v>
+      </c>
+      <c r="C174" s="3" t="s">
+        <v>1505</v>
+      </c>
+      <c r="D174" s="3" t="s">
+        <v>1506</v>
+      </c>
+      <c r="E174" s="3" t="s">
+        <v>1507</v>
+      </c>
+      <c r="F174" s="3" t="s">
+        <v>1508</v>
+      </c>
+      <c r="G174" s="3" t="s">
+        <v>1509</v>
+      </c>
+      <c r="H174" s="3" t="s">
+        <v>1510</v>
+      </c>
+      <c r="I174" s="3" t="s">
+        <v>1511</v>
+      </c>
+      <c r="J174" s="3" t="s">
+        <v>1512</v>
+      </c>
+      <c r="K174" s="3">
+        <v>1</v>
+      </c>
+      <c r="L174" s="3" t="s">
+        <v>1513</v>
+      </c>
+    </row>
+    <row r="175" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A175" s="3" t="s">
+        <v>1495</v>
+      </c>
+      <c r="B175" s="3" t="s">
+        <v>1514</v>
+      </c>
+      <c r="C175" s="3" t="s">
+        <v>1515</v>
+      </c>
+      <c r="D175" s="3" t="s">
+        <v>1516</v>
+      </c>
+      <c r="E175" s="3" t="s">
+        <v>1603</v>
+      </c>
+      <c r="F175" s="3" t="s">
+        <v>1517</v>
+      </c>
+      <c r="G175" s="3" t="s">
+        <v>1518</v>
+      </c>
+      <c r="H175" s="3" t="s">
+        <v>1519</v>
+      </c>
+      <c r="I175" s="3" t="s">
+        <v>1520</v>
+      </c>
+      <c r="J175" s="3" t="s">
+        <v>1521</v>
+      </c>
+      <c r="K175" s="3">
+        <v>1</v>
+      </c>
+      <c r="L175" s="3" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="176" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A176" s="3" t="s">
+        <v>1495</v>
+      </c>
+      <c r="B176" s="3" t="s">
+        <v>1514</v>
+      </c>
+      <c r="C176" s="3" t="s">
+        <v>1523</v>
+      </c>
+      <c r="D176" s="3" t="s">
+        <v>1524</v>
+      </c>
+      <c r="E176" s="3" t="s">
+        <v>1525</v>
+      </c>
+      <c r="F176" s="3" t="s">
+        <v>1526</v>
+      </c>
+      <c r="G176" s="3" t="s">
+        <v>1527</v>
+      </c>
+      <c r="H176" s="3" t="s">
+        <v>1528</v>
+      </c>
+      <c r="I176" s="3" t="s">
+        <v>1529</v>
+      </c>
+      <c r="J176" s="3" t="s">
+        <v>1024</v>
+      </c>
+      <c r="K176" s="3">
+        <v>1</v>
+      </c>
+      <c r="L176" s="3" t="s">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="177" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A177" s="3" t="s">
+        <v>1495</v>
+      </c>
+      <c r="B177" s="3" t="s">
+        <v>1531</v>
+      </c>
+      <c r="C177" s="3" t="s">
+        <v>1532</v>
+      </c>
+      <c r="D177" s="3" t="s">
+        <v>1533</v>
+      </c>
+      <c r="E177" s="3" t="s">
+        <v>1534</v>
+      </c>
+      <c r="F177" s="3" t="s">
+        <v>1535</v>
+      </c>
+      <c r="G177" s="3" t="s">
+        <v>1244</v>
+      </c>
+      <c r="H177" s="3" t="s">
+        <v>1536</v>
+      </c>
+      <c r="I177" s="3" t="s">
+        <v>1537</v>
+      </c>
+      <c r="J177" s="3" t="s">
+        <v>1538</v>
+      </c>
+      <c r="K177" s="3">
+        <v>1</v>
+      </c>
+      <c r="L177" s="3" t="s">
+        <v>1539</v>
+      </c>
+    </row>
+    <row r="178" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A178" s="3" t="s">
+        <v>1495</v>
+      </c>
+      <c r="B178" s="3" t="s">
+        <v>1531</v>
+      </c>
+      <c r="C178" s="3" t="s">
+        <v>1540</v>
+      </c>
+      <c r="D178" s="3" t="s">
+        <v>1541</v>
+      </c>
+      <c r="E178" s="3" t="s">
+        <v>1542</v>
+      </c>
+      <c r="F178" s="3" t="s">
+        <v>1543</v>
+      </c>
+      <c r="G178" s="3" t="s">
+        <v>1544</v>
+      </c>
+      <c r="H178" s="3" t="s">
+        <v>1545</v>
+      </c>
+      <c r="I178" s="3" t="s">
+        <v>1546</v>
+      </c>
+      <c r="J178" s="3" t="s">
+        <v>1547</v>
+      </c>
+      <c r="K178" s="3">
+        <v>1</v>
+      </c>
+      <c r="L178" s="3" t="s">
+        <v>1548</v>
+      </c>
+    </row>
+    <row r="179" spans="1:12" ht="33.75" x14ac:dyDescent="0.2">
+      <c r="A179" s="3" t="s">
+        <v>1495</v>
+      </c>
+      <c r="B179" s="3" t="s">
+        <v>1549</v>
+      </c>
+      <c r="C179" s="3" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D179" s="3" t="s">
+        <v>1551</v>
+      </c>
+      <c r="E179" s="3" t="s">
+        <v>1552</v>
+      </c>
+      <c r="F179" s="3" t="s">
+        <v>1553</v>
+      </c>
+      <c r="G179" s="3" t="s">
+        <v>1554</v>
+      </c>
+      <c r="H179" s="3" t="s">
+        <v>1555</v>
+      </c>
+      <c r="I179" s="3" t="s">
+        <v>1556</v>
+      </c>
+      <c r="J179" s="3" t="s">
+        <v>1557</v>
+      </c>
+      <c r="K179" s="3">
+        <v>1</v>
+      </c>
+      <c r="L179" s="3" t="s">
+        <v>1558</v>
+      </c>
+    </row>
+    <row r="180" spans="1:12" ht="33.75" x14ac:dyDescent="0.2">
+      <c r="A180" s="3" t="s">
+        <v>1495</v>
+      </c>
+      <c r="B180" s="3" t="s">
+        <v>1549</v>
+      </c>
+      <c r="C180" s="3" t="s">
+        <v>1559</v>
+      </c>
+      <c r="D180" s="3" t="s">
+        <v>1560</v>
+      </c>
+      <c r="E180" s="3" t="s">
+        <v>1561</v>
+      </c>
+      <c r="F180" s="3" t="s">
+        <v>1562</v>
+      </c>
+      <c r="G180" s="3" t="s">
+        <v>1563</v>
+      </c>
+      <c r="H180" s="3" t="s">
+        <v>1564</v>
+      </c>
+      <c r="I180" s="3" t="s">
+        <v>1565</v>
+      </c>
+      <c r="J180" s="3" t="s">
+        <v>1566</v>
+      </c>
+      <c r="K180" s="3">
+        <v>1</v>
+      </c>
+      <c r="L180" s="3" t="s">
+        <v>1567</v>
+      </c>
+    </row>
+    <row r="181" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A181" s="3" t="s">
+        <v>1495</v>
+      </c>
+      <c r="B181" s="3" t="s">
+        <v>1568</v>
+      </c>
+      <c r="C181" s="3" t="s">
+        <v>1569</v>
+      </c>
+      <c r="D181" s="3" t="s">
+        <v>1570</v>
+      </c>
+      <c r="E181" s="3" t="s">
+        <v>1571</v>
+      </c>
+      <c r="F181" s="3" t="s">
+        <v>1572</v>
+      </c>
+      <c r="G181" s="3" t="s">
+        <v>1573</v>
+      </c>
+      <c r="H181" s="3" t="s">
+        <v>1574</v>
+      </c>
+      <c r="I181" s="3" t="s">
+        <v>1575</v>
+      </c>
+      <c r="J181" s="3" t="s">
+        <v>1576</v>
+      </c>
+      <c r="K181" s="3">
+        <v>1</v>
+      </c>
+      <c r="L181" s="3" t="s">
+        <v>1567</v>
+      </c>
+    </row>
+    <row r="182" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A182" s="3" t="s">
+        <v>1495</v>
+      </c>
+      <c r="B182" s="3" t="s">
+        <v>1568</v>
+      </c>
+      <c r="C182" s="3" t="s">
+        <v>1577</v>
+      </c>
+      <c r="D182" s="3" t="s">
+        <v>1578</v>
+      </c>
+      <c r="E182" s="3" t="s">
+        <v>1579</v>
+      </c>
+      <c r="F182" s="3" t="s">
+        <v>1580</v>
+      </c>
+      <c r="G182" s="3" t="s">
+        <v>1581</v>
+      </c>
+      <c r="H182" s="3" t="s">
+        <v>1582</v>
+      </c>
+      <c r="I182" s="3" t="s">
+        <v>1583</v>
+      </c>
+      <c r="J182" s="3" t="s">
+        <v>1584</v>
+      </c>
+      <c r="K182" s="3">
+        <v>1</v>
+      </c>
+      <c r="L182" s="3" t="s">
+        <v>1585</v>
+      </c>
+    </row>
+    <row r="183" spans="1:12" ht="33.75" x14ac:dyDescent="0.2">
+      <c r="A183" s="3" t="s">
+        <v>1495</v>
+      </c>
+      <c r="B183" s="3" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C183" s="3" t="s">
+        <v>1586</v>
+      </c>
+      <c r="D183" s="3" t="s">
+        <v>1587</v>
+      </c>
+      <c r="E183" s="3" t="s">
+        <v>1588</v>
+      </c>
+      <c r="F183" s="3" t="s">
+        <v>1589</v>
+      </c>
+      <c r="G183" s="3" t="s">
+        <v>1590</v>
+      </c>
+      <c r="H183" s="3" t="s">
+        <v>1591</v>
+      </c>
+      <c r="I183" s="3" t="s">
+        <v>1592</v>
+      </c>
+      <c r="J183" s="3" t="s">
+        <v>1593</v>
+      </c>
+      <c r="K183" s="3">
+        <v>1</v>
+      </c>
+      <c r="L183" s="3" t="s">
+        <v>1594</v>
+      </c>
+    </row>
+    <row r="184" spans="1:12" ht="56.25" x14ac:dyDescent="0.2">
+      <c r="A184" s="3" t="s">
+        <v>1495</v>
+      </c>
+      <c r="B184" s="3" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C184" s="3" t="s">
+        <v>1595</v>
+      </c>
+      <c r="D184" s="3" t="s">
+        <v>1596</v>
+      </c>
+      <c r="E184" s="3" t="s">
+        <v>1597</v>
+      </c>
+      <c r="F184" s="3" t="s">
+        <v>1598</v>
+      </c>
+      <c r="G184" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="H184" s="3" t="s">
+        <v>1599</v>
+      </c>
+      <c r="I184" s="3" t="s">
+        <v>1600</v>
+      </c>
+      <c r="J184" s="3" t="s">
+        <v>1601</v>
+      </c>
+      <c r="K184" s="3">
+        <v>1</v>
+      </c>
+      <c r="L184" s="3" t="s">
+        <v>1602</v>
+      </c>
+    </row>
+    <row r="185" spans="1:12" ht="67.5" x14ac:dyDescent="0.2">
+      <c r="A185" s="3" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B185" s="3" t="s">
+        <v>872</v>
+      </c>
+      <c r="C185" s="3" t="s">
+        <v>1605</v>
+      </c>
+      <c r="D185" s="3" t="s">
+        <v>1606</v>
+      </c>
+      <c r="E185" s="3" t="s">
+        <v>1607</v>
+      </c>
+      <c r="F185" s="3" t="s">
+        <v>1608</v>
+      </c>
+      <c r="G185" s="3" t="s">
+        <v>1609</v>
+      </c>
+      <c r="H185" s="3" t="s">
+        <v>1610</v>
+      </c>
+      <c r="I185" s="3" t="s">
+        <v>1611</v>
+      </c>
+      <c r="J185" s="3" t="s">
+        <v>1612</v>
+      </c>
+      <c r="K185" s="3">
+        <v>1</v>
+      </c>
+      <c r="L185" s="3" t="s">
+        <v>1613</v>
+      </c>
+    </row>
+    <row r="186" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A186" s="3" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B186" s="3" t="s">
+        <v>872</v>
+      </c>
+      <c r="C186" s="3" t="s">
+        <v>1614</v>
+      </c>
+      <c r="D186" s="3" t="s">
+        <v>1615</v>
+      </c>
+      <c r="E186" s="3" t="s">
+        <v>1616</v>
+      </c>
+      <c r="F186" s="3" t="s">
+        <v>1617</v>
+      </c>
+      <c r="G186" s="3" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H186" s="3" t="s">
+        <v>1619</v>
+      </c>
+      <c r="I186" s="3" t="s">
+        <v>1620</v>
+      </c>
+      <c r="J186" s="3" t="s">
+        <v>1621</v>
+      </c>
+      <c r="K186" s="3">
+        <v>1</v>
+      </c>
+      <c r="L186" s="3" t="s">
+        <v>1622</v>
+      </c>
+    </row>
+    <row r="187" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A187" s="3" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B187" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="C187" s="3" t="s">
+        <v>1623</v>
+      </c>
+      <c r="D187" s="3" t="s">
+        <v>1624</v>
+      </c>
+      <c r="E187" s="3" t="s">
+        <v>1625</v>
+      </c>
+      <c r="F187" s="3" t="s">
+        <v>1626</v>
+      </c>
+      <c r="G187" s="3" t="s">
+        <v>1627</v>
+      </c>
+      <c r="H187" s="3" t="s">
+        <v>1628</v>
+      </c>
+      <c r="I187" s="3" t="s">
+        <v>1629</v>
+      </c>
+      <c r="J187" s="3" t="s">
+        <v>1630</v>
+      </c>
+      <c r="K187" s="3">
+        <v>1</v>
+      </c>
+      <c r="L187" s="3" t="s">
+        <v>1631</v>
+      </c>
+    </row>
+    <row r="188" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A188" s="3" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B188" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="C188" s="3" t="s">
+        <v>1632</v>
+      </c>
+      <c r="D188" s="3" t="s">
+        <v>1633</v>
+      </c>
+      <c r="E188" s="3" t="s">
+        <v>1634</v>
+      </c>
+      <c r="F188" s="3" t="s">
+        <v>1635</v>
+      </c>
+      <c r="G188" s="3" t="s">
+        <v>1636</v>
+      </c>
+      <c r="H188" s="3" t="s">
+        <v>1637</v>
+      </c>
+      <c r="I188" s="3" t="s">
+        <v>1638</v>
+      </c>
+      <c r="J188" s="3" t="s">
+        <v>1639</v>
+      </c>
+      <c r="K188" s="3">
+        <v>1</v>
+      </c>
+      <c r="L188" s="3" t="s">
+        <v>1640</v>
+      </c>
+    </row>
+    <row r="189" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A189" s="3" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B189" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C189" s="3" t="s">
+        <v>1641</v>
+      </c>
+      <c r="D189" s="3" t="s">
+        <v>1642</v>
+      </c>
+      <c r="E189" s="3" t="s">
+        <v>1643</v>
+      </c>
+      <c r="F189" s="3" t="s">
+        <v>1644</v>
+      </c>
+      <c r="G189" s="3" t="s">
+        <v>1590</v>
+      </c>
+      <c r="H189" s="3" t="s">
+        <v>1645</v>
+      </c>
+      <c r="I189" s="3" t="s">
+        <v>1646</v>
+      </c>
+      <c r="J189" s="3" t="s">
+        <v>1647</v>
+      </c>
+      <c r="K189" s="3">
+        <v>1</v>
+      </c>
+      <c r="L189" s="3" t="s">
+        <v>1648</v>
+      </c>
+    </row>
+    <row r="190" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A190" s="3" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B190" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C190" s="3" t="s">
+        <v>1649</v>
+      </c>
+      <c r="D190" s="3" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E190" s="3" t="s">
+        <v>1651</v>
+      </c>
+      <c r="F190" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="G190" s="3" t="s">
+        <v>1653</v>
+      </c>
+      <c r="H190" s="3" t="s">
+        <v>1654</v>
+      </c>
+      <c r="I190" s="3" t="s">
+        <v>1655</v>
+      </c>
+      <c r="J190" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="K190" s="3">
+        <v>1</v>
+      </c>
+      <c r="L190" s="3" t="s">
+        <v>1657</v>
+      </c>
+    </row>
+    <row r="191" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A191" s="3" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B191" s="3" t="s">
+        <v>955</v>
+      </c>
+      <c r="C191" s="3" t="s">
+        <v>1658</v>
+      </c>
+      <c r="D191" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="E191" s="3" t="s">
+        <v>1660</v>
+      </c>
+      <c r="F191" s="3" t="s">
+        <v>1661</v>
+      </c>
+      <c r="G191" s="3" t="s">
+        <v>1662</v>
+      </c>
+      <c r="H191" s="3" t="s">
+        <v>1663</v>
+      </c>
+      <c r="I191" s="3" t="s">
+        <v>1664</v>
+      </c>
+      <c r="J191" s="3" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K191" s="3">
+        <v>1</v>
+      </c>
+      <c r="L191" s="3" t="s">
+        <v>1665</v>
+      </c>
+    </row>
+    <row r="192" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A192" s="3" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B192" s="3" t="s">
+        <v>955</v>
+      </c>
+      <c r="C192" s="3" t="s">
+        <v>1666</v>
+      </c>
+      <c r="D192" s="3" t="s">
+        <v>1667</v>
+      </c>
+      <c r="E192" s="3" t="s">
+        <v>1668</v>
+      </c>
+      <c r="F192" s="3" t="s">
+        <v>1669</v>
+      </c>
+      <c r="G192" s="3" t="s">
+        <v>969</v>
+      </c>
+      <c r="H192" s="3" t="s">
+        <v>1670</v>
+      </c>
+      <c r="I192" s="3" t="s">
+        <v>971</v>
+      </c>
+      <c r="J192" s="3" t="s">
+        <v>972</v>
+      </c>
+      <c r="K192" s="3">
+        <v>1</v>
+      </c>
+      <c r="L192" s="3" t="s">
+        <v>1671</v>
+      </c>
+    </row>
+    <row r="193" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A193" s="3" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B193" s="3" t="s">
+        <v>1672</v>
+      </c>
+      <c r="C193" s="3" t="s">
+        <v>1673</v>
+      </c>
+      <c r="D193" s="3" t="s">
+        <v>1674</v>
+      </c>
+      <c r="E193" s="3" t="s">
+        <v>1675</v>
+      </c>
+      <c r="F193" s="3" t="s">
+        <v>1676</v>
+      </c>
+      <c r="G193" s="3" t="s">
+        <v>1677</v>
+      </c>
+      <c r="H193" s="3" t="s">
+        <v>1678</v>
+      </c>
+      <c r="I193" s="3" t="s">
+        <v>1679</v>
+      </c>
+      <c r="J193" s="3" t="s">
+        <v>1680</v>
+      </c>
+      <c r="K193" s="3">
+        <v>1</v>
+      </c>
+      <c r="L193" s="3" t="s">
+        <v>1681</v>
+      </c>
+    </row>
+    <row r="194" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A194" s="3" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B194" s="3" t="s">
+        <v>1672</v>
+      </c>
+      <c r="C194" s="3" t="s">
+        <v>1682</v>
+      </c>
+      <c r="D194" s="3" t="s">
+        <v>1683</v>
+      </c>
+      <c r="E194" s="3" t="s">
+        <v>1684</v>
+      </c>
+      <c r="F194" s="3" t="s">
+        <v>1685</v>
+      </c>
+      <c r="G194" s="3" t="s">
+        <v>1686</v>
+      </c>
+      <c r="H194" s="3" t="s">
+        <v>1687</v>
+      </c>
+      <c r="I194" s="3" t="s">
+        <v>1688</v>
+      </c>
+      <c r="J194" s="3" t="s">
+        <v>1689</v>
+      </c>
+      <c r="K194" s="3">
+        <v>1</v>
+      </c>
+      <c r="L194" s="3" t="s">
+        <v>1690</v>
+      </c>
+    </row>
+    <row r="195" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A195" s="3" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B195" s="3" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C195" s="3" t="s">
+        <v>1691</v>
+      </c>
+      <c r="D195" s="3" t="s">
+        <v>1692</v>
+      </c>
+      <c r="E195" s="3" t="s">
+        <v>1693</v>
+      </c>
+      <c r="F195" s="3" t="s">
+        <v>1694</v>
+      </c>
+      <c r="G195" s="3" t="s">
+        <v>1695</v>
+      </c>
+      <c r="H195" s="3" t="s">
+        <v>1696</v>
+      </c>
+      <c r="I195" s="3" t="s">
+        <v>1697</v>
+      </c>
+      <c r="J195" s="3" t="s">
+        <v>1698</v>
+      </c>
+      <c r="K195" s="3">
+        <v>1</v>
+      </c>
+      <c r="L195" s="3" t="s">
+        <v>1699</v>
+      </c>
+    </row>
+    <row r="196" spans="1:12" ht="45" x14ac:dyDescent="0.2">
+      <c r="A196" s="3" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B196" s="3" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C196" s="3" t="s">
+        <v>1700</v>
+      </c>
+      <c r="D196" s="3" t="s">
+        <v>1701</v>
+      </c>
+      <c r="E196" s="3" t="s">
+        <v>1702</v>
+      </c>
+      <c r="F196" s="3" t="s">
+        <v>1703</v>
+      </c>
+      <c r="G196" s="3" t="s">
+        <v>1704</v>
+      </c>
+      <c r="H196" s="3" t="s">
+        <v>1705</v>
+      </c>
+      <c r="I196" s="3" t="s">
+        <v>1706</v>
+      </c>
+      <c r="J196" s="3" t="s">
+        <v>1707</v>
+      </c>
+      <c r="K196" s="3">
+        <v>1</v>
+      </c>
+      <c r="L196" s="3" t="s">
+        <v>1708</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:L70" xr:uid="{3594F0E7-7C10-4023-9C47-66514D348C6C}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>